--- a/data/properties.xlsx
+++ b/data/properties.xlsx
@@ -1220,7 +1220,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -1245,7 +1244,6 @@
       <c r="R2" t="n">
         <v>2001</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
         <v>13</v>
       </c>
@@ -1260,7 +1258,6 @@
           <t>Gross</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
         <v>26000000</v>
       </c>
@@ -1288,7 +1285,6 @@
           <t>Gateway Industrial REIT</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -1322,11 +1318,6 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr">
         <is>
           <t>Gateway Industrial REIT</t>
@@ -1337,11 +1328,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
         <v>6.4</v>
       </c>
@@ -1359,8 +1345,6 @@
           <t>2 x 5yr</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
           <t>2031-04</t>
@@ -1381,16 +1365,6 @@
       <c r="BN2" t="n">
         <v>0.63</v>
       </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
       <c r="BY2" t="inlineStr">
         <is>
           <t>Family Office Capital</t>
@@ -1402,34 +1376,6 @@
       <c r="CA2" t="n">
         <v>29471909</v>
       </c>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="inlineStr"/>
-      <c r="CI2" t="inlineStr"/>
-      <c r="CJ2" t="inlineStr"/>
-      <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="inlineStr"/>
-      <c r="DC2" t="inlineStr"/>
       <c r="DD2" t="n">
         <v>94</v>
       </c>
@@ -1471,11 +1417,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr"/>
-      <c r="DP2" t="inlineStr"/>
-      <c r="DQ2" t="inlineStr"/>
-      <c r="DR2" t="inlineStr"/>
-      <c r="DS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1529,11 +1470,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Minneapolis CBD</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -1558,7 +1494,6 @@
       <c r="R3" t="n">
         <v>1980</v>
       </c>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
         <v>17</v>
       </c>
@@ -1603,7 +1538,6 @@
           <t>Gateway Industrial REIT</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -1637,11 +1571,6 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr">
         <is>
           <t>Gateway Industrial REIT</t>
@@ -1652,11 +1581,6 @@
           <t>Heartland REIT</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
         <v>9.9</v>
       </c>
@@ -1702,17 +1626,6 @@
       <c r="BN3" t="n">
         <v>0.45</v>
       </c>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
       <c r="BZ3" t="n">
         <v>100</v>
       </c>
@@ -1735,7 +1648,6 @@
           <t>Platinum</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="n">
         <v>6000</v>
       </c>
@@ -1757,40 +1669,6 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="inlineStr"/>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="inlineStr"/>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="inlineStr"/>
-      <c r="DC3" t="inlineStr"/>
-      <c r="DD3" t="inlineStr"/>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="inlineStr"/>
-      <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="inlineStr"/>
-      <c r="DJ3" t="inlineStr"/>
-      <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="inlineStr"/>
-      <c r="DM3" t="inlineStr"/>
-      <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="inlineStr"/>
-      <c r="DP3" t="inlineStr"/>
-      <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="inlineStr"/>
-      <c r="DS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1844,7 +1722,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -1869,7 +1746,6 @@
       <c r="R4" t="n">
         <v>1938</v>
       </c>
-      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
         <v>10</v>
       </c>
@@ -1914,7 +1790,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -1963,8 +1838,6 @@
           <t>2027-Q4</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="inlineStr">
         <is>
           <t>Mall Street Partners</t>
@@ -2079,7 +1952,6 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr"/>
       <c r="BZ4" t="n">
         <v>100</v>
       </c>
@@ -2128,40 +2000,6 @@
           <t>Surface</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
-      <c r="DC4" t="inlineStr"/>
-      <c r="DD4" t="inlineStr"/>
-      <c r="DE4" t="inlineStr"/>
-      <c r="DF4" t="inlineStr"/>
-      <c r="DG4" t="inlineStr"/>
-      <c r="DH4" t="inlineStr"/>
-      <c r="DI4" t="inlineStr"/>
-      <c r="DJ4" t="inlineStr"/>
-      <c r="DK4" t="inlineStr"/>
-      <c r="DL4" t="inlineStr"/>
-      <c r="DM4" t="inlineStr"/>
-      <c r="DN4" t="inlineStr"/>
-      <c r="DO4" t="inlineStr"/>
-      <c r="DP4" t="inlineStr"/>
-      <c r="DQ4" t="inlineStr"/>
-      <c r="DR4" t="inlineStr"/>
-      <c r="DS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2215,7 +2053,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -2257,7 +2094,6 @@
           <t>Net</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
         <v>38000000</v>
       </c>
@@ -2285,7 +2121,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -2303,13 +2138,6 @@
       <c r="AK5" t="n">
         <v>39</v>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
         <v>4150000</v>
       </c>
@@ -2397,8 +2225,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="n">
         <v>25</v>
       </c>
@@ -2479,40 +2305,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="inlineStr"/>
-      <c r="DH5" t="inlineStr"/>
-      <c r="DI5" t="inlineStr"/>
-      <c r="DJ5" t="inlineStr"/>
-      <c r="DK5" t="inlineStr"/>
-      <c r="DL5" t="inlineStr"/>
-      <c r="DM5" t="inlineStr"/>
-      <c r="DN5" t="inlineStr"/>
-      <c r="DO5" t="inlineStr"/>
-      <c r="DP5" t="inlineStr"/>
-      <c r="DQ5" t="inlineStr"/>
-      <c r="DR5" t="inlineStr"/>
-      <c r="DS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2566,11 +2358,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Minneapolis CBD</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -2595,7 +2382,6 @@
       <c r="R6" t="n">
         <v>2020</v>
       </c>
-      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>8</v>
       </c>
@@ -2640,7 +2426,6 @@
           <t>Twin Cities Ventures</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -2658,15 +2443,6 @@
       <c r="AK6" t="n">
         <v>24</v>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="inlineStr">
         <is>
           <t>Twin Cities Ventures</t>
@@ -2677,11 +2453,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -2699,8 +2470,6 @@
           <t>1 x 5yr</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
           <t>2028-07</t>
@@ -2721,16 +2490,6 @@
       <c r="BN6" t="n">
         <v>1.63</v>
       </c>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
-      <c r="BX6" t="inlineStr"/>
       <c r="BY6" t="inlineStr">
         <is>
           <t>Family Office Capital</t>
@@ -2742,34 +2501,6 @@
       <c r="CA6" t="n">
         <v>84269412</v>
       </c>
-      <c r="CB6" t="inlineStr"/>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
-      <c r="CE6" t="inlineStr"/>
-      <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="inlineStr"/>
-      <c r="CH6" t="inlineStr"/>
-      <c r="CI6" t="inlineStr"/>
-      <c r="CJ6" t="inlineStr"/>
-      <c r="CK6" t="inlineStr"/>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
-      <c r="CN6" t="inlineStr"/>
-      <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="inlineStr"/>
-      <c r="CQ6" t="inlineStr"/>
-      <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="inlineStr"/>
-      <c r="CY6" t="inlineStr"/>
-      <c r="CZ6" t="inlineStr"/>
-      <c r="DA6" t="inlineStr"/>
-      <c r="DB6" t="inlineStr"/>
-      <c r="DC6" t="inlineStr"/>
       <c r="DD6" t="n">
         <v>100</v>
       </c>
@@ -2811,11 +2542,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO6" t="inlineStr"/>
-      <c r="DP6" t="inlineStr"/>
-      <c r="DQ6" t="inlineStr"/>
-      <c r="DR6" t="inlineStr"/>
-      <c r="DS6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2869,11 +2595,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Minneapolis CBD</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -2898,7 +2619,6 @@
       <c r="R7" t="n">
         <v>1920</v>
       </c>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
         <v>8</v>
       </c>
@@ -2943,7 +2663,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -2961,15 +2680,6 @@
       <c r="AK7" t="n">
         <v>23</v>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="inlineStr">
         <is>
           <t>SouthPoint Advisors</t>
@@ -3016,8 +2726,6 @@
           <t>2 x 5yr</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
           <t>2033-08</t>
@@ -3089,34 +2797,6 @@
       <c r="CA7" t="n">
         <v>348249093</v>
       </c>
-      <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr"/>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr"/>
-      <c r="CI7" t="inlineStr"/>
-      <c r="CJ7" t="inlineStr"/>
-      <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
-      <c r="CN7" t="inlineStr"/>
-      <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="inlineStr"/>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="inlineStr"/>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
       <c r="DD7" t="n">
         <v>278</v>
       </c>
@@ -3158,11 +2838,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO7" t="inlineStr"/>
-      <c r="DP7" t="inlineStr"/>
-      <c r="DQ7" t="inlineStr"/>
-      <c r="DR7" t="inlineStr"/>
-      <c r="DS7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3216,11 +2891,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Minneapolis CBD</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -3245,7 +2915,6 @@
       <c r="R8" t="n">
         <v>2001</v>
       </c>
-      <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
         <v>1</v>
       </c>
@@ -3290,7 +2959,6 @@
           <t>Gateway Industrial REIT</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -3308,15 +2976,6 @@
       <c r="AK8" t="n">
         <v>1</v>
       </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="inlineStr">
         <is>
           <t>Gateway Industrial REIT</t>
@@ -3327,11 +2986,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
         <v>7.7</v>
       </c>
@@ -3377,16 +3031,6 @@
       <c r="BN8" t="n">
         <v>0.84</v>
       </c>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-      <c r="BW8" t="inlineStr"/>
-      <c r="BX8" t="inlineStr"/>
       <c r="BY8" t="inlineStr">
         <is>
           <t>State Pension Co-Invest</t>
@@ -3398,30 +3042,11 @@
       <c r="CA8" t="n">
         <v>270619100</v>
       </c>
-      <c r="CB8" t="inlineStr"/>
-      <c r="CC8" t="inlineStr"/>
-      <c r="CD8" t="inlineStr"/>
-      <c r="CE8" t="inlineStr"/>
       <c r="CF8" t="inlineStr">
         <is>
           <t>HomeGoods (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr"/>
-      <c r="CH8" t="inlineStr"/>
-      <c r="CI8" t="inlineStr"/>
-      <c r="CJ8" t="inlineStr"/>
-      <c r="CK8" t="inlineStr"/>
-      <c r="CL8" t="inlineStr"/>
-      <c r="CM8" t="inlineStr"/>
-      <c r="CN8" t="inlineStr"/>
-      <c r="CO8" t="inlineStr"/>
-      <c r="CP8" t="inlineStr"/>
-      <c r="CQ8" t="inlineStr"/>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
       <c r="CV8" t="inlineStr">
         <is>
           <t>Strip</t>
@@ -3454,22 +3079,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DD8" t="inlineStr"/>
-      <c r="DE8" t="inlineStr"/>
-      <c r="DF8" t="inlineStr"/>
-      <c r="DG8" t="inlineStr"/>
-      <c r="DH8" t="inlineStr"/>
-      <c r="DI8" t="inlineStr"/>
-      <c r="DJ8" t="inlineStr"/>
-      <c r="DK8" t="inlineStr"/>
-      <c r="DL8" t="inlineStr"/>
-      <c r="DM8" t="inlineStr"/>
-      <c r="DN8" t="inlineStr"/>
-      <c r="DO8" t="inlineStr"/>
-      <c r="DP8" t="inlineStr"/>
-      <c r="DQ8" t="inlineStr"/>
-      <c r="DR8" t="inlineStr"/>
-      <c r="DS8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3523,11 +3132,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Minneapolis CBD</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Under Construction</t>
@@ -3552,7 +3156,6 @@
       <c r="R9" t="n">
         <v>1946</v>
       </c>
-      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
         <v>33</v>
       </c>
@@ -3567,10 +3170,6 @@
           <t>Net</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
         <v>4069</v>
       </c>
@@ -3587,7 +3186,6 @@
           <t>Sample Holdings LLC</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -3636,10 +3234,6 @@
           <t>2027-Q4</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
           <t>Agency (Fannie) SAMPLE</t>
@@ -3709,8 +3303,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr"/>
-      <c r="BQ9" t="inlineStr"/>
       <c r="BR9" t="n">
         <v>30</v>
       </c>
@@ -3746,7 +3338,6 @@
       <c r="BZ9" t="n">
         <v>50</v>
       </c>
-      <c r="CA9" t="inlineStr"/>
       <c r="CB9" t="n">
         <v>27800</v>
       </c>
@@ -3789,40 +3380,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr"/>
-      <c r="CM9" t="inlineStr"/>
-      <c r="CN9" t="inlineStr"/>
-      <c r="CO9" t="inlineStr"/>
-      <c r="CP9" t="inlineStr"/>
-      <c r="CQ9" t="inlineStr"/>
-      <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
-      <c r="CV9" t="inlineStr"/>
-      <c r="CW9" t="inlineStr"/>
-      <c r="CX9" t="inlineStr"/>
-      <c r="CY9" t="inlineStr"/>
-      <c r="CZ9" t="inlineStr"/>
-      <c r="DA9" t="inlineStr"/>
-      <c r="DB9" t="inlineStr"/>
-      <c r="DC9" t="inlineStr"/>
-      <c r="DD9" t="inlineStr"/>
-      <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr"/>
-      <c r="DG9" t="inlineStr"/>
-      <c r="DH9" t="inlineStr"/>
-      <c r="DI9" t="inlineStr"/>
-      <c r="DJ9" t="inlineStr"/>
-      <c r="DK9" t="inlineStr"/>
-      <c r="DL9" t="inlineStr"/>
-      <c r="DM9" t="inlineStr"/>
-      <c r="DN9" t="inlineStr"/>
-      <c r="DO9" t="inlineStr"/>
-      <c r="DP9" t="inlineStr"/>
-      <c r="DQ9" t="inlineStr"/>
-      <c r="DR9" t="inlineStr"/>
-      <c r="DS9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3876,11 +3433,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Minneapolis CBD</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -3905,7 +3457,6 @@
       <c r="R10" t="n">
         <v>1946</v>
       </c>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
         <v>25</v>
       </c>
@@ -3950,7 +3501,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -3968,15 +3518,6 @@
       <c r="AK10" t="n">
         <v>1</v>
       </c>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr">
         <is>
           <t>Riverbend Residential</t>
@@ -3987,11 +3528,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
         <v>10.5</v>
       </c>
@@ -4037,17 +3573,6 @@
       <c r="BN10" t="n">
         <v>0.89</v>
       </c>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
-      <c r="BQ10" t="inlineStr"/>
-      <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
-      <c r="BT10" t="inlineStr"/>
-      <c r="BU10" t="inlineStr"/>
-      <c r="BV10" t="inlineStr"/>
-      <c r="BW10" t="inlineStr"/>
-      <c r="BX10" t="inlineStr"/>
-      <c r="BY10" t="inlineStr"/>
       <c r="BZ10" t="n">
         <v>100</v>
       </c>
@@ -4070,7 +3595,6 @@
           <t>Silver</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="n">
         <v>0</v>
       </c>
@@ -4092,40 +3616,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
-      <c r="CN10" t="inlineStr"/>
-      <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="inlineStr"/>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="inlineStr"/>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="inlineStr"/>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="inlineStr"/>
-      <c r="CX10" t="inlineStr"/>
-      <c r="CY10" t="inlineStr"/>
-      <c r="CZ10" t="inlineStr"/>
-      <c r="DA10" t="inlineStr"/>
-      <c r="DB10" t="inlineStr"/>
-      <c r="DC10" t="inlineStr"/>
-      <c r="DD10" t="inlineStr"/>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
-      <c r="DG10" t="inlineStr"/>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="inlineStr"/>
-      <c r="DJ10" t="inlineStr"/>
-      <c r="DK10" t="inlineStr"/>
-      <c r="DL10" t="inlineStr"/>
-      <c r="DM10" t="inlineStr"/>
-      <c r="DN10" t="inlineStr"/>
-      <c r="DO10" t="inlineStr"/>
-      <c r="DP10" t="inlineStr"/>
-      <c r="DQ10" t="inlineStr"/>
-      <c r="DR10" t="inlineStr"/>
-      <c r="DS10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4179,7 +3669,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -4251,7 +3740,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -4285,9 +3773,6 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
         <v>275000</v>
       </c>
@@ -4375,8 +3860,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr"/>
-      <c r="BQ11" t="inlineStr"/>
       <c r="BR11" t="n">
         <v>25</v>
       </c>
@@ -4457,40 +3940,6 @@
           <t>Surface</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr"/>
-      <c r="CM11" t="inlineStr"/>
-      <c r="CN11" t="inlineStr"/>
-      <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="inlineStr"/>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
-      <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="inlineStr"/>
-      <c r="DA11" t="inlineStr"/>
-      <c r="DB11" t="inlineStr"/>
-      <c r="DC11" t="inlineStr"/>
-      <c r="DD11" t="inlineStr"/>
-      <c r="DE11" t="inlineStr"/>
-      <c r="DF11" t="inlineStr"/>
-      <c r="DG11" t="inlineStr"/>
-      <c r="DH11" t="inlineStr"/>
-      <c r="DI11" t="inlineStr"/>
-      <c r="DJ11" t="inlineStr"/>
-      <c r="DK11" t="inlineStr"/>
-      <c r="DL11" t="inlineStr"/>
-      <c r="DM11" t="inlineStr"/>
-      <c r="DN11" t="inlineStr"/>
-      <c r="DO11" t="inlineStr"/>
-      <c r="DP11" t="inlineStr"/>
-      <c r="DQ11" t="inlineStr"/>
-      <c r="DR11" t="inlineStr"/>
-      <c r="DS11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4544,11 +3993,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>St. Paul CBD</t>
-        </is>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -4620,7 +4064,6 @@
           <t>Lakes Capital Group</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -4638,13 +4081,6 @@
       <c r="AK12" t="n">
         <v>1</v>
       </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
         <v>9525000</v>
       </c>
@@ -4820,40 +4256,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
-      <c r="CN12" t="inlineStr"/>
-      <c r="CO12" t="inlineStr"/>
-      <c r="CP12" t="inlineStr"/>
-      <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="inlineStr"/>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr"/>
-      <c r="CV12" t="inlineStr"/>
-      <c r="CW12" t="inlineStr"/>
-      <c r="CX12" t="inlineStr"/>
-      <c r="CY12" t="inlineStr"/>
-      <c r="CZ12" t="inlineStr"/>
-      <c r="DA12" t="inlineStr"/>
-      <c r="DB12" t="inlineStr"/>
-      <c r="DC12" t="inlineStr"/>
-      <c r="DD12" t="inlineStr"/>
-      <c r="DE12" t="inlineStr"/>
-      <c r="DF12" t="inlineStr"/>
-      <c r="DG12" t="inlineStr"/>
-      <c r="DH12" t="inlineStr"/>
-      <c r="DI12" t="inlineStr"/>
-      <c r="DJ12" t="inlineStr"/>
-      <c r="DK12" t="inlineStr"/>
-      <c r="DL12" t="inlineStr"/>
-      <c r="DM12" t="inlineStr"/>
-      <c r="DN12" t="inlineStr"/>
-      <c r="DO12" t="inlineStr"/>
-      <c r="DP12" t="inlineStr"/>
-      <c r="DQ12" t="inlineStr"/>
-      <c r="DR12" t="inlineStr"/>
-      <c r="DS12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4907,7 +4309,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -4932,7 +4333,6 @@
       <c r="R13" t="n">
         <v>1954</v>
       </c>
-      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
         <v>20</v>
       </c>
@@ -4950,9 +4350,6 @@
       <c r="X13" t="n">
         <v>5.34</v>
       </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="n">
         <v>4048</v>
       </c>
@@ -4969,7 +4366,6 @@
           <t>Sample Holdings LLC</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -4987,17 +4383,6 @@
       <c r="AK13" t="n">
         <v>34</v>
       </c>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
           <t>Agency (Fannie) SAMPLE</t>
@@ -5102,11 +4487,9 @@
           <t>2023-01</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="n">
         <v>100</v>
       </c>
-      <c r="CA13" t="inlineStr"/>
       <c r="CB13" t="n">
         <v>48200</v>
       </c>
@@ -5123,7 +4506,6 @@
           <t>Certified</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr"/>
       <c r="CG13" t="n">
         <v>12000</v>
       </c>
@@ -5145,40 +4527,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL13" t="inlineStr"/>
-      <c r="CM13" t="inlineStr"/>
-      <c r="CN13" t="inlineStr"/>
-      <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="inlineStr"/>
-      <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="inlineStr"/>
-      <c r="CZ13" t="inlineStr"/>
-      <c r="DA13" t="inlineStr"/>
-      <c r="DB13" t="inlineStr"/>
-      <c r="DC13" t="inlineStr"/>
-      <c r="DD13" t="inlineStr"/>
-      <c r="DE13" t="inlineStr"/>
-      <c r="DF13" t="inlineStr"/>
-      <c r="DG13" t="inlineStr"/>
-      <c r="DH13" t="inlineStr"/>
-      <c r="DI13" t="inlineStr"/>
-      <c r="DJ13" t="inlineStr"/>
-      <c r="DK13" t="inlineStr"/>
-      <c r="DL13" t="inlineStr"/>
-      <c r="DM13" t="inlineStr"/>
-      <c r="DN13" t="inlineStr"/>
-      <c r="DO13" t="inlineStr"/>
-      <c r="DP13" t="inlineStr"/>
-      <c r="DQ13" t="inlineStr"/>
-      <c r="DR13" t="inlineStr"/>
-      <c r="DS13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5232,7 +4580,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -5257,7 +4604,6 @@
       <c r="R14" t="n">
         <v>1928</v>
       </c>
-      <c r="S14" t="inlineStr"/>
       <c r="T14" t="n">
         <v>16</v>
       </c>
@@ -5275,9 +4621,6 @@
       <c r="X14" t="n">
         <v>8.07</v>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
         <v>1398</v>
       </c>
@@ -5294,7 +4637,6 @@
           <t>Lakes Capital Group</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -5328,13 +4670,6 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
           <t>First Sample Bank</t>
@@ -5371,8 +4706,6 @@
           <t>1 x 5yr</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
           <t>2027-10</t>
@@ -5398,8 +4731,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr"/>
-      <c r="BQ14" t="inlineStr"/>
       <c r="BR14" t="n">
         <v>25</v>
       </c>
@@ -5427,39 +4758,9 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="n">
         <v>100</v>
       </c>
-      <c r="CA14" t="inlineStr"/>
-      <c r="CB14" t="inlineStr"/>
-      <c r="CC14" t="inlineStr"/>
-      <c r="CD14" t="inlineStr"/>
-      <c r="CE14" t="inlineStr"/>
-      <c r="CF14" t="inlineStr"/>
-      <c r="CG14" t="inlineStr"/>
-      <c r="CH14" t="inlineStr"/>
-      <c r="CI14" t="inlineStr"/>
-      <c r="CJ14" t="inlineStr"/>
-      <c r="CK14" t="inlineStr"/>
-      <c r="CL14" t="inlineStr"/>
-      <c r="CM14" t="inlineStr"/>
-      <c r="CN14" t="inlineStr"/>
-      <c r="CO14" t="inlineStr"/>
-      <c r="CP14" t="inlineStr"/>
-      <c r="CQ14" t="inlineStr"/>
-      <c r="CR14" t="inlineStr"/>
-      <c r="CS14" t="inlineStr"/>
-      <c r="CT14" t="inlineStr"/>
-      <c r="CU14" t="inlineStr"/>
-      <c r="CV14" t="inlineStr"/>
-      <c r="CW14" t="inlineStr"/>
-      <c r="CX14" t="inlineStr"/>
-      <c r="CY14" t="inlineStr"/>
-      <c r="CZ14" t="inlineStr"/>
-      <c r="DA14" t="inlineStr"/>
-      <c r="DB14" t="inlineStr"/>
-      <c r="DC14" t="inlineStr"/>
       <c r="DD14" t="n">
         <v>402</v>
       </c>
@@ -5501,11 +4802,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO14" t="inlineStr"/>
-      <c r="DP14" t="inlineStr"/>
-      <c r="DQ14" t="inlineStr"/>
-      <c r="DR14" t="inlineStr"/>
-      <c r="DS14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5559,7 +4855,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -5584,7 +4879,6 @@
       <c r="R15" t="n">
         <v>1962</v>
       </c>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
         <v>26</v>
       </c>
@@ -5629,7 +4923,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -5663,11 +4956,6 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="inlineStr">
         <is>
           <t>Mall Street Partners</t>
@@ -5678,11 +4966,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -5728,17 +5011,6 @@
       <c r="BN15" t="n">
         <v>1.05</v>
       </c>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
-      <c r="BQ15" t="inlineStr"/>
-      <c r="BR15" t="inlineStr"/>
-      <c r="BS15" t="inlineStr"/>
-      <c r="BT15" t="inlineStr"/>
-      <c r="BU15" t="inlineStr"/>
-      <c r="BV15" t="inlineStr"/>
-      <c r="BW15" t="inlineStr"/>
-      <c r="BX15" t="inlineStr"/>
-      <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="n">
         <v>100</v>
       </c>
@@ -5787,40 +5059,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL15" t="inlineStr"/>
-      <c r="CM15" t="inlineStr"/>
-      <c r="CN15" t="inlineStr"/>
-      <c r="CO15" t="inlineStr"/>
-      <c r="CP15" t="inlineStr"/>
-      <c r="CQ15" t="inlineStr"/>
-      <c r="CR15" t="inlineStr"/>
-      <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="inlineStr"/>
-      <c r="CU15" t="inlineStr"/>
-      <c r="CV15" t="inlineStr"/>
-      <c r="CW15" t="inlineStr"/>
-      <c r="CX15" t="inlineStr"/>
-      <c r="CY15" t="inlineStr"/>
-      <c r="CZ15" t="inlineStr"/>
-      <c r="DA15" t="inlineStr"/>
-      <c r="DB15" t="inlineStr"/>
-      <c r="DC15" t="inlineStr"/>
-      <c r="DD15" t="inlineStr"/>
-      <c r="DE15" t="inlineStr"/>
-      <c r="DF15" t="inlineStr"/>
-      <c r="DG15" t="inlineStr"/>
-      <c r="DH15" t="inlineStr"/>
-      <c r="DI15" t="inlineStr"/>
-      <c r="DJ15" t="inlineStr"/>
-      <c r="DK15" t="inlineStr"/>
-      <c r="DL15" t="inlineStr"/>
-      <c r="DM15" t="inlineStr"/>
-      <c r="DN15" t="inlineStr"/>
-      <c r="DO15" t="inlineStr"/>
-      <c r="DP15" t="inlineStr"/>
-      <c r="DQ15" t="inlineStr"/>
-      <c r="DR15" t="inlineStr"/>
-      <c r="DS15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5874,7 +5112,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -5899,7 +5136,6 @@
       <c r="R16" t="n">
         <v>2010</v>
       </c>
-      <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
         <v>31</v>
       </c>
@@ -5917,9 +5153,6 @@
       <c r="X16" t="n">
         <v>7.23</v>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="n">
         <v>524</v>
       </c>
@@ -5936,7 +5169,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -5970,13 +5202,6 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
           <t>First Sample Bank</t>
@@ -6046,8 +5271,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr"/>
-      <c r="BQ16" t="inlineStr"/>
       <c r="BR16" t="n">
         <v>0</v>
       </c>
@@ -6083,7 +5306,6 @@
       <c r="BZ16" t="n">
         <v>75</v>
       </c>
-      <c r="CA16" t="inlineStr"/>
       <c r="CB16" t="n">
         <v>7800</v>
       </c>
@@ -6126,40 +5348,6 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="CL16" t="inlineStr"/>
-      <c r="CM16" t="inlineStr"/>
-      <c r="CN16" t="inlineStr"/>
-      <c r="CO16" t="inlineStr"/>
-      <c r="CP16" t="inlineStr"/>
-      <c r="CQ16" t="inlineStr"/>
-      <c r="CR16" t="inlineStr"/>
-      <c r="CS16" t="inlineStr"/>
-      <c r="CT16" t="inlineStr"/>
-      <c r="CU16" t="inlineStr"/>
-      <c r="CV16" t="inlineStr"/>
-      <c r="CW16" t="inlineStr"/>
-      <c r="CX16" t="inlineStr"/>
-      <c r="CY16" t="inlineStr"/>
-      <c r="CZ16" t="inlineStr"/>
-      <c r="DA16" t="inlineStr"/>
-      <c r="DB16" t="inlineStr"/>
-      <c r="DC16" t="inlineStr"/>
-      <c r="DD16" t="inlineStr"/>
-      <c r="DE16" t="inlineStr"/>
-      <c r="DF16" t="inlineStr"/>
-      <c r="DG16" t="inlineStr"/>
-      <c r="DH16" t="inlineStr"/>
-      <c r="DI16" t="inlineStr"/>
-      <c r="DJ16" t="inlineStr"/>
-      <c r="DK16" t="inlineStr"/>
-      <c r="DL16" t="inlineStr"/>
-      <c r="DM16" t="inlineStr"/>
-      <c r="DN16" t="inlineStr"/>
-      <c r="DO16" t="inlineStr"/>
-      <c r="DP16" t="inlineStr"/>
-      <c r="DQ16" t="inlineStr"/>
-      <c r="DR16" t="inlineStr"/>
-      <c r="DS16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6213,7 +5401,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -6285,7 +5472,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -6352,11 +5538,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="n">
         <v>5.9</v>
       </c>
@@ -6402,16 +5583,6 @@
       <c r="BN17" t="n">
         <v>0.51</v>
       </c>
-      <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr"/>
-      <c r="BQ17" t="inlineStr"/>
-      <c r="BR17" t="inlineStr"/>
-      <c r="BS17" t="inlineStr"/>
-      <c r="BT17" t="inlineStr"/>
-      <c r="BU17" t="inlineStr"/>
-      <c r="BV17" t="inlineStr"/>
-      <c r="BW17" t="inlineStr"/>
-      <c r="BX17" t="inlineStr"/>
       <c r="BY17" t="inlineStr">
         <is>
           <t>Family Office Capital</t>
@@ -6423,30 +5594,11 @@
       <c r="CA17" t="n">
         <v>273556818</v>
       </c>
-      <c r="CB17" t="inlineStr"/>
-      <c r="CC17" t="inlineStr"/>
-      <c r="CD17" t="inlineStr"/>
-      <c r="CE17" t="inlineStr"/>
       <c r="CF17" t="inlineStr">
         <is>
           <t>HomeGoods (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG17" t="inlineStr"/>
-      <c r="CH17" t="inlineStr"/>
-      <c r="CI17" t="inlineStr"/>
-      <c r="CJ17" t="inlineStr"/>
-      <c r="CK17" t="inlineStr"/>
-      <c r="CL17" t="inlineStr"/>
-      <c r="CM17" t="inlineStr"/>
-      <c r="CN17" t="inlineStr"/>
-      <c r="CO17" t="inlineStr"/>
-      <c r="CP17" t="inlineStr"/>
-      <c r="CQ17" t="inlineStr"/>
-      <c r="CR17" t="inlineStr"/>
-      <c r="CS17" t="inlineStr"/>
-      <c r="CT17" t="inlineStr"/>
-      <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="inlineStr">
         <is>
           <t>Neighborhood</t>
@@ -6479,22 +5631,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD17" t="inlineStr"/>
-      <c r="DE17" t="inlineStr"/>
-      <c r="DF17" t="inlineStr"/>
-      <c r="DG17" t="inlineStr"/>
-      <c r="DH17" t="inlineStr"/>
-      <c r="DI17" t="inlineStr"/>
-      <c r="DJ17" t="inlineStr"/>
-      <c r="DK17" t="inlineStr"/>
-      <c r="DL17" t="inlineStr"/>
-      <c r="DM17" t="inlineStr"/>
-      <c r="DN17" t="inlineStr"/>
-      <c r="DO17" t="inlineStr"/>
-      <c r="DP17" t="inlineStr"/>
-      <c r="DQ17" t="inlineStr"/>
-      <c r="DR17" t="inlineStr"/>
-      <c r="DS17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6548,11 +5684,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Midway</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -6577,7 +5708,6 @@
       <c r="R18" t="n">
         <v>2005</v>
       </c>
-      <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
         <v>1</v>
       </c>
@@ -6622,7 +5752,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -6656,11 +5785,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="inlineStr">
         <is>
           <t>Riverbend Residential</t>
@@ -6786,16 +5910,6 @@
       <c r="CA18" t="n">
         <v>202347310</v>
       </c>
-      <c r="CB18" t="inlineStr"/>
-      <c r="CC18" t="inlineStr"/>
-      <c r="CD18" t="inlineStr"/>
-      <c r="CE18" t="inlineStr"/>
-      <c r="CF18" t="inlineStr"/>
-      <c r="CG18" t="inlineStr"/>
-      <c r="CH18" t="inlineStr"/>
-      <c r="CI18" t="inlineStr"/>
-      <c r="CJ18" t="inlineStr"/>
-      <c r="CK18" t="inlineStr"/>
       <c r="CL18" t="n">
         <v>40</v>
       </c>
@@ -6832,30 +5946,6 @@
       <c r="CU18" t="n">
         <v>130</v>
       </c>
-      <c r="CV18" t="inlineStr"/>
-      <c r="CW18" t="inlineStr"/>
-      <c r="CX18" t="inlineStr"/>
-      <c r="CY18" t="inlineStr"/>
-      <c r="CZ18" t="inlineStr"/>
-      <c r="DA18" t="inlineStr"/>
-      <c r="DB18" t="inlineStr"/>
-      <c r="DC18" t="inlineStr"/>
-      <c r="DD18" t="inlineStr"/>
-      <c r="DE18" t="inlineStr"/>
-      <c r="DF18" t="inlineStr"/>
-      <c r="DG18" t="inlineStr"/>
-      <c r="DH18" t="inlineStr"/>
-      <c r="DI18" t="inlineStr"/>
-      <c r="DJ18" t="inlineStr"/>
-      <c r="DK18" t="inlineStr"/>
-      <c r="DL18" t="inlineStr"/>
-      <c r="DM18" t="inlineStr"/>
-      <c r="DN18" t="inlineStr"/>
-      <c r="DO18" t="inlineStr"/>
-      <c r="DP18" t="inlineStr"/>
-      <c r="DQ18" t="inlineStr"/>
-      <c r="DR18" t="inlineStr"/>
-      <c r="DS18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6909,11 +5999,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Midway</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -6938,7 +6023,6 @@
       <c r="R19" t="n">
         <v>1969</v>
       </c>
-      <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
         <v>1</v>
       </c>
@@ -6956,9 +6040,6 @@
       <c r="X19" t="n">
         <v>8.32</v>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="n">
         <v>811</v>
       </c>
@@ -6975,7 +6056,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -6993,17 +6073,6 @@
       <c r="AK19" t="n">
         <v>1</v>
       </c>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
           <t>Agency (Fannie) SAMPLE</t>
@@ -7073,8 +6142,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP19" t="inlineStr"/>
-      <c r="BQ19" t="inlineStr"/>
       <c r="BR19" t="n">
         <v>0</v>
       </c>
@@ -7102,35 +6169,14 @@
           <t>2022-06</t>
         </is>
       </c>
-      <c r="BY19" t="inlineStr"/>
       <c r="BZ19" t="n">
         <v>100</v>
       </c>
-      <c r="CA19" t="inlineStr"/>
-      <c r="CB19" t="inlineStr"/>
-      <c r="CC19" t="inlineStr"/>
-      <c r="CD19" t="inlineStr"/>
-      <c r="CE19" t="inlineStr"/>
       <c r="CF19" t="inlineStr">
         <is>
           <t>Target (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG19" t="inlineStr"/>
-      <c r="CH19" t="inlineStr"/>
-      <c r="CI19" t="inlineStr"/>
-      <c r="CJ19" t="inlineStr"/>
-      <c r="CK19" t="inlineStr"/>
-      <c r="CL19" t="inlineStr"/>
-      <c r="CM19" t="inlineStr"/>
-      <c r="CN19" t="inlineStr"/>
-      <c r="CO19" t="inlineStr"/>
-      <c r="CP19" t="inlineStr"/>
-      <c r="CQ19" t="inlineStr"/>
-      <c r="CR19" t="inlineStr"/>
-      <c r="CS19" t="inlineStr"/>
-      <c r="CT19" t="inlineStr"/>
-      <c r="CU19" t="inlineStr"/>
       <c r="CV19" t="inlineStr">
         <is>
           <t>Neighborhood</t>
@@ -7163,22 +6209,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD19" t="inlineStr"/>
-      <c r="DE19" t="inlineStr"/>
-      <c r="DF19" t="inlineStr"/>
-      <c r="DG19" t="inlineStr"/>
-      <c r="DH19" t="inlineStr"/>
-      <c r="DI19" t="inlineStr"/>
-      <c r="DJ19" t="inlineStr"/>
-      <c r="DK19" t="inlineStr"/>
-      <c r="DL19" t="inlineStr"/>
-      <c r="DM19" t="inlineStr"/>
-      <c r="DN19" t="inlineStr"/>
-      <c r="DO19" t="inlineStr"/>
-      <c r="DP19" t="inlineStr"/>
-      <c r="DQ19" t="inlineStr"/>
-      <c r="DR19" t="inlineStr"/>
-      <c r="DS19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7232,7 +6262,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -7257,7 +6286,6 @@
       <c r="R20" t="n">
         <v>2018</v>
       </c>
-      <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
         <v>1</v>
       </c>
@@ -7302,7 +6330,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -7320,15 +6347,6 @@
       <c r="AK20" t="n">
         <v>23</v>
       </c>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
       <c r="AU20" t="inlineStr">
         <is>
           <t>Capitol City Assets</t>
@@ -7408,8 +6426,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr"/>
-      <c r="BQ20" t="inlineStr"/>
       <c r="BR20" t="n">
         <v>30</v>
       </c>
@@ -7448,16 +6464,6 @@
       <c r="CA20" t="n">
         <v>296252281</v>
       </c>
-      <c r="CB20" t="inlineStr"/>
-      <c r="CC20" t="inlineStr"/>
-      <c r="CD20" t="inlineStr"/>
-      <c r="CE20" t="inlineStr"/>
-      <c r="CF20" t="inlineStr"/>
-      <c r="CG20" t="inlineStr"/>
-      <c r="CH20" t="inlineStr"/>
-      <c r="CI20" t="inlineStr"/>
-      <c r="CJ20" t="inlineStr"/>
-      <c r="CK20" t="inlineStr"/>
       <c r="CL20" t="n">
         <v>24</v>
       </c>
@@ -7494,30 +6500,6 @@
       <c r="CU20" t="n">
         <v>185</v>
       </c>
-      <c r="CV20" t="inlineStr"/>
-      <c r="CW20" t="inlineStr"/>
-      <c r="CX20" t="inlineStr"/>
-      <c r="CY20" t="inlineStr"/>
-      <c r="CZ20" t="inlineStr"/>
-      <c r="DA20" t="inlineStr"/>
-      <c r="DB20" t="inlineStr"/>
-      <c r="DC20" t="inlineStr"/>
-      <c r="DD20" t="inlineStr"/>
-      <c r="DE20" t="inlineStr"/>
-      <c r="DF20" t="inlineStr"/>
-      <c r="DG20" t="inlineStr"/>
-      <c r="DH20" t="inlineStr"/>
-      <c r="DI20" t="inlineStr"/>
-      <c r="DJ20" t="inlineStr"/>
-      <c r="DK20" t="inlineStr"/>
-      <c r="DL20" t="inlineStr"/>
-      <c r="DM20" t="inlineStr"/>
-      <c r="DN20" t="inlineStr"/>
-      <c r="DO20" t="inlineStr"/>
-      <c r="DP20" t="inlineStr"/>
-      <c r="DQ20" t="inlineStr"/>
-      <c r="DR20" t="inlineStr"/>
-      <c r="DS20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7571,7 +6553,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -7643,7 +6624,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -7661,13 +6641,6 @@
       <c r="AK21" t="n">
         <v>32</v>
       </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="n">
         <v>2600000</v>
       </c>
@@ -7790,23 +6763,12 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="BY21" t="inlineStr"/>
       <c r="BZ21" t="n">
         <v>100</v>
       </c>
       <c r="CA21" t="n">
         <v>132368064</v>
       </c>
-      <c r="CB21" t="inlineStr"/>
-      <c r="CC21" t="inlineStr"/>
-      <c r="CD21" t="inlineStr"/>
-      <c r="CE21" t="inlineStr"/>
-      <c r="CF21" t="inlineStr"/>
-      <c r="CG21" t="inlineStr"/>
-      <c r="CH21" t="inlineStr"/>
-      <c r="CI21" t="inlineStr"/>
-      <c r="CJ21" t="inlineStr"/>
-      <c r="CK21" t="inlineStr"/>
       <c r="CL21" t="n">
         <v>16</v>
       </c>
@@ -7843,30 +6805,6 @@
       <c r="CU21" t="n">
         <v>110</v>
       </c>
-      <c r="CV21" t="inlineStr"/>
-      <c r="CW21" t="inlineStr"/>
-      <c r="CX21" t="inlineStr"/>
-      <c r="CY21" t="inlineStr"/>
-      <c r="CZ21" t="inlineStr"/>
-      <c r="DA21" t="inlineStr"/>
-      <c r="DB21" t="inlineStr"/>
-      <c r="DC21" t="inlineStr"/>
-      <c r="DD21" t="inlineStr"/>
-      <c r="DE21" t="inlineStr"/>
-      <c r="DF21" t="inlineStr"/>
-      <c r="DG21" t="inlineStr"/>
-      <c r="DH21" t="inlineStr"/>
-      <c r="DI21" t="inlineStr"/>
-      <c r="DJ21" t="inlineStr"/>
-      <c r="DK21" t="inlineStr"/>
-      <c r="DL21" t="inlineStr"/>
-      <c r="DM21" t="inlineStr"/>
-      <c r="DN21" t="inlineStr"/>
-      <c r="DO21" t="inlineStr"/>
-      <c r="DP21" t="inlineStr"/>
-      <c r="DQ21" t="inlineStr"/>
-      <c r="DR21" t="inlineStr"/>
-      <c r="DS21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7915,30 +6853,19 @@
           <t>Land</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Existing</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Family Office</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
         <v>22.9</v>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
         <v>259000000</v>
       </c>
@@ -7947,9 +6874,6 @@
           <t>2025-09-01</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
           <t>R-6</t>
@@ -7960,25 +6884,11 @@
           <t>Lakes Capital Group</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
       <c r="AU22" t="inlineStr">
         <is>
           <t>Lakes Capital Group</t>
@@ -7989,82 +6899,15 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
-      <c r="BG22" t="inlineStr"/>
-      <c r="BH22" t="inlineStr"/>
-      <c r="BI22" t="inlineStr"/>
-      <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="inlineStr"/>
-      <c r="BL22" t="inlineStr"/>
-      <c r="BM22" t="inlineStr"/>
-      <c r="BN22" t="inlineStr"/>
-      <c r="BO22" t="inlineStr"/>
-      <c r="BP22" t="inlineStr"/>
-      <c r="BQ22" t="inlineStr"/>
-      <c r="BR22" t="inlineStr"/>
-      <c r="BS22" t="inlineStr"/>
-      <c r="BT22" t="inlineStr"/>
-      <c r="BU22" t="inlineStr"/>
-      <c r="BV22" t="inlineStr"/>
-      <c r="BW22" t="inlineStr"/>
-      <c r="BX22" t="inlineStr"/>
-      <c r="BY22" t="inlineStr"/>
       <c r="BZ22" t="n">
         <v>100</v>
       </c>
       <c r="CA22" t="n">
         <v>286793218</v>
       </c>
-      <c r="CB22" t="inlineStr"/>
-      <c r="CC22" t="inlineStr"/>
-      <c r="CD22" t="inlineStr"/>
-      <c r="CE22" t="inlineStr"/>
-      <c r="CF22" t="inlineStr"/>
-      <c r="CG22" t="inlineStr"/>
-      <c r="CH22" t="inlineStr"/>
-      <c r="CI22" t="inlineStr"/>
-      <c r="CJ22" t="inlineStr"/>
-      <c r="CK22" t="inlineStr"/>
-      <c r="CL22" t="inlineStr"/>
-      <c r="CM22" t="inlineStr"/>
-      <c r="CN22" t="inlineStr"/>
-      <c r="CO22" t="inlineStr"/>
-      <c r="CP22" t="inlineStr"/>
-      <c r="CQ22" t="inlineStr"/>
-      <c r="CR22" t="inlineStr"/>
-      <c r="CS22" t="inlineStr"/>
-      <c r="CT22" t="inlineStr"/>
-      <c r="CU22" t="inlineStr"/>
-      <c r="CV22" t="inlineStr"/>
-      <c r="CW22" t="inlineStr"/>
       <c r="CX22" t="n">
         <v>1200</v>
       </c>
-      <c r="CY22" t="inlineStr"/>
-      <c r="CZ22" t="inlineStr"/>
-      <c r="DA22" t="inlineStr"/>
-      <c r="DB22" t="inlineStr"/>
-      <c r="DC22" t="inlineStr"/>
-      <c r="DD22" t="inlineStr"/>
-      <c r="DE22" t="inlineStr"/>
-      <c r="DF22" t="inlineStr"/>
-      <c r="DG22" t="inlineStr"/>
-      <c r="DH22" t="inlineStr"/>
-      <c r="DI22" t="inlineStr"/>
-      <c r="DJ22" t="inlineStr"/>
-      <c r="DK22" t="inlineStr"/>
-      <c r="DL22" t="inlineStr"/>
-      <c r="DM22" t="inlineStr"/>
-      <c r="DN22" t="inlineStr"/>
       <c r="DO22" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -8143,7 +6986,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -8168,7 +7010,6 @@
       <c r="R23" t="n">
         <v>2002</v>
       </c>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="n">
         <v>1</v>
       </c>
@@ -8213,7 +7054,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -8231,15 +7071,6 @@
       <c r="AK23" t="n">
         <v>24</v>
       </c>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="inlineStr">
         <is>
           <t>SouthPoint Advisors</t>
@@ -8250,11 +7081,6 @@
           <t>Sample Holdings LLC</t>
         </is>
       </c>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="n">
         <v>6</v>
       </c>
@@ -8300,16 +7126,6 @@
       <c r="BN23" t="n">
         <v>1.28</v>
       </c>
-      <c r="BO23" t="inlineStr"/>
-      <c r="BP23" t="inlineStr"/>
-      <c r="BQ23" t="inlineStr"/>
-      <c r="BR23" t="inlineStr"/>
-      <c r="BS23" t="inlineStr"/>
-      <c r="BT23" t="inlineStr"/>
-      <c r="BU23" t="inlineStr"/>
-      <c r="BV23" t="inlineStr"/>
-      <c r="BW23" t="inlineStr"/>
-      <c r="BX23" t="inlineStr"/>
       <c r="BY23" t="inlineStr">
         <is>
           <t>Sample Insurance GA</t>
@@ -8321,16 +7137,6 @@
       <c r="CA23" t="n">
         <v>30007175</v>
       </c>
-      <c r="CB23" t="inlineStr"/>
-      <c r="CC23" t="inlineStr"/>
-      <c r="CD23" t="inlineStr"/>
-      <c r="CE23" t="inlineStr"/>
-      <c r="CF23" t="inlineStr"/>
-      <c r="CG23" t="inlineStr"/>
-      <c r="CH23" t="inlineStr"/>
-      <c r="CI23" t="inlineStr"/>
-      <c r="CJ23" t="inlineStr"/>
-      <c r="CK23" t="inlineStr"/>
       <c r="CL23" t="n">
         <v>36</v>
       </c>
@@ -8367,30 +7173,6 @@
       <c r="CU23" t="n">
         <v>90</v>
       </c>
-      <c r="CV23" t="inlineStr"/>
-      <c r="CW23" t="inlineStr"/>
-      <c r="CX23" t="inlineStr"/>
-      <c r="CY23" t="inlineStr"/>
-      <c r="CZ23" t="inlineStr"/>
-      <c r="DA23" t="inlineStr"/>
-      <c r="DB23" t="inlineStr"/>
-      <c r="DC23" t="inlineStr"/>
-      <c r="DD23" t="inlineStr"/>
-      <c r="DE23" t="inlineStr"/>
-      <c r="DF23" t="inlineStr"/>
-      <c r="DG23" t="inlineStr"/>
-      <c r="DH23" t="inlineStr"/>
-      <c r="DI23" t="inlineStr"/>
-      <c r="DJ23" t="inlineStr"/>
-      <c r="DK23" t="inlineStr"/>
-      <c r="DL23" t="inlineStr"/>
-      <c r="DM23" t="inlineStr"/>
-      <c r="DN23" t="inlineStr"/>
-      <c r="DO23" t="inlineStr"/>
-      <c r="DP23" t="inlineStr"/>
-      <c r="DQ23" t="inlineStr"/>
-      <c r="DR23" t="inlineStr"/>
-      <c r="DS23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8444,11 +7226,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>I-494 Corridor</t>
-        </is>
-      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -8520,7 +7297,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -8554,9 +7330,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="n">
         <v>8425000</v>
       </c>
@@ -8575,11 +7348,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
-      <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="n">
         <v>3.2</v>
       </c>
@@ -8625,16 +7393,6 @@
       <c r="BN24" t="n">
         <v>1.98</v>
       </c>
-      <c r="BO24" t="inlineStr"/>
-      <c r="BP24" t="inlineStr"/>
-      <c r="BQ24" t="inlineStr"/>
-      <c r="BR24" t="inlineStr"/>
-      <c r="BS24" t="inlineStr"/>
-      <c r="BT24" t="inlineStr"/>
-      <c r="BU24" t="inlineStr"/>
-      <c r="BV24" t="inlineStr"/>
-      <c r="BW24" t="inlineStr"/>
-      <c r="BX24" t="inlineStr"/>
       <c r="BY24" t="inlineStr">
         <is>
           <t>State Pension Co-Invest</t>
@@ -8688,40 +7446,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL24" t="inlineStr"/>
-      <c r="CM24" t="inlineStr"/>
-      <c r="CN24" t="inlineStr"/>
-      <c r="CO24" t="inlineStr"/>
-      <c r="CP24" t="inlineStr"/>
-      <c r="CQ24" t="inlineStr"/>
-      <c r="CR24" t="inlineStr"/>
-      <c r="CS24" t="inlineStr"/>
-      <c r="CT24" t="inlineStr"/>
-      <c r="CU24" t="inlineStr"/>
-      <c r="CV24" t="inlineStr"/>
-      <c r="CW24" t="inlineStr"/>
-      <c r="CX24" t="inlineStr"/>
-      <c r="CY24" t="inlineStr"/>
-      <c r="CZ24" t="inlineStr"/>
-      <c r="DA24" t="inlineStr"/>
-      <c r="DB24" t="inlineStr"/>
-      <c r="DC24" t="inlineStr"/>
-      <c r="DD24" t="inlineStr"/>
-      <c r="DE24" t="inlineStr"/>
-      <c r="DF24" t="inlineStr"/>
-      <c r="DG24" t="inlineStr"/>
-      <c r="DH24" t="inlineStr"/>
-      <c r="DI24" t="inlineStr"/>
-      <c r="DJ24" t="inlineStr"/>
-      <c r="DK24" t="inlineStr"/>
-      <c r="DL24" t="inlineStr"/>
-      <c r="DM24" t="inlineStr"/>
-      <c r="DN24" t="inlineStr"/>
-      <c r="DO24" t="inlineStr"/>
-      <c r="DP24" t="inlineStr"/>
-      <c r="DQ24" t="inlineStr"/>
-      <c r="DR24" t="inlineStr"/>
-      <c r="DS24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8775,7 +7499,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -8800,7 +7523,6 @@
       <c r="R25" t="n">
         <v>1974</v>
       </c>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="n">
         <v>2</v>
       </c>
@@ -8845,7 +7567,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -8879,11 +7600,6 @@
           <t>Planned</t>
         </is>
       </c>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
       <c r="AU25" t="inlineStr">
         <is>
           <t>Capitol City Assets</t>
@@ -8963,8 +7679,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP25" t="inlineStr"/>
-      <c r="BQ25" t="inlineStr"/>
       <c r="BR25" t="n">
         <v>30</v>
       </c>
@@ -9003,30 +7717,11 @@
       <c r="CA25" t="n">
         <v>330502672</v>
       </c>
-      <c r="CB25" t="inlineStr"/>
-      <c r="CC25" t="inlineStr"/>
-      <c r="CD25" t="inlineStr"/>
-      <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="inlineStr">
         <is>
           <t>Cub Foods (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG25" t="inlineStr"/>
-      <c r="CH25" t="inlineStr"/>
-      <c r="CI25" t="inlineStr"/>
-      <c r="CJ25" t="inlineStr"/>
-      <c r="CK25" t="inlineStr"/>
-      <c r="CL25" t="inlineStr"/>
-      <c r="CM25" t="inlineStr"/>
-      <c r="CN25" t="inlineStr"/>
-      <c r="CO25" t="inlineStr"/>
-      <c r="CP25" t="inlineStr"/>
-      <c r="CQ25" t="inlineStr"/>
-      <c r="CR25" t="inlineStr"/>
-      <c r="CS25" t="inlineStr"/>
-      <c r="CT25" t="inlineStr"/>
-      <c r="CU25" t="inlineStr"/>
       <c r="CV25" t="inlineStr">
         <is>
           <t>Lifestyle</t>
@@ -9059,22 +7754,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD25" t="inlineStr"/>
-      <c r="DE25" t="inlineStr"/>
-      <c r="DF25" t="inlineStr"/>
-      <c r="DG25" t="inlineStr"/>
-      <c r="DH25" t="inlineStr"/>
-      <c r="DI25" t="inlineStr"/>
-      <c r="DJ25" t="inlineStr"/>
-      <c r="DK25" t="inlineStr"/>
-      <c r="DL25" t="inlineStr"/>
-      <c r="DM25" t="inlineStr"/>
-      <c r="DN25" t="inlineStr"/>
-      <c r="DO25" t="inlineStr"/>
-      <c r="DP25" t="inlineStr"/>
-      <c r="DQ25" t="inlineStr"/>
-      <c r="DR25" t="inlineStr"/>
-      <c r="DS25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9128,7 +7807,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -9153,7 +7831,6 @@
       <c r="R26" t="n">
         <v>1996</v>
       </c>
-      <c r="S26" t="inlineStr"/>
       <c r="T26" t="n">
         <v>1</v>
       </c>
@@ -9168,7 +7845,6 @@
           <t>NNN</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
         <v>193000000</v>
       </c>
@@ -9196,7 +7872,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -9214,15 +7889,6 @@
       <c r="AK26" t="n">
         <v>26</v>
       </c>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
       <c r="AU26" t="inlineStr">
         <is>
           <t>Mall Street Partners</t>
@@ -9337,23 +8003,12 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="BY26" t="inlineStr"/>
       <c r="BZ26" t="n">
         <v>100</v>
       </c>
       <c r="CA26" t="n">
         <v>195182945</v>
       </c>
-      <c r="CB26" t="inlineStr"/>
-      <c r="CC26" t="inlineStr"/>
-      <c r="CD26" t="inlineStr"/>
-      <c r="CE26" t="inlineStr"/>
-      <c r="CF26" t="inlineStr"/>
-      <c r="CG26" t="inlineStr"/>
-      <c r="CH26" t="inlineStr"/>
-      <c r="CI26" t="inlineStr"/>
-      <c r="CJ26" t="inlineStr"/>
-      <c r="CK26" t="inlineStr"/>
       <c r="CL26" t="n">
         <v>24</v>
       </c>
@@ -9390,30 +8045,6 @@
       <c r="CU26" t="n">
         <v>185</v>
       </c>
-      <c r="CV26" t="inlineStr"/>
-      <c r="CW26" t="inlineStr"/>
-      <c r="CX26" t="inlineStr"/>
-      <c r="CY26" t="inlineStr"/>
-      <c r="CZ26" t="inlineStr"/>
-      <c r="DA26" t="inlineStr"/>
-      <c r="DB26" t="inlineStr"/>
-      <c r="DC26" t="inlineStr"/>
-      <c r="DD26" t="inlineStr"/>
-      <c r="DE26" t="inlineStr"/>
-      <c r="DF26" t="inlineStr"/>
-      <c r="DG26" t="inlineStr"/>
-      <c r="DH26" t="inlineStr"/>
-      <c r="DI26" t="inlineStr"/>
-      <c r="DJ26" t="inlineStr"/>
-      <c r="DK26" t="inlineStr"/>
-      <c r="DL26" t="inlineStr"/>
-      <c r="DM26" t="inlineStr"/>
-      <c r="DN26" t="inlineStr"/>
-      <c r="DO26" t="inlineStr"/>
-      <c r="DP26" t="inlineStr"/>
-      <c r="DQ26" t="inlineStr"/>
-      <c r="DR26" t="inlineStr"/>
-      <c r="DS26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9467,11 +8098,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>I-494 Corridor</t>
-        </is>
-      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -9496,7 +8122,6 @@
       <c r="R27" t="n">
         <v>1995</v>
       </c>
-      <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
         <v>1</v>
       </c>
@@ -9541,7 +8166,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -9575,11 +8199,6 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
       <c r="AU27" t="inlineStr">
         <is>
           <t>North Fund IV</t>
@@ -9590,11 +8209,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="n">
         <v>9.5</v>
       </c>
@@ -9640,16 +8254,6 @@
       <c r="BN27" t="n">
         <v>1.07</v>
       </c>
-      <c r="BO27" t="inlineStr"/>
-      <c r="BP27" t="inlineStr"/>
-      <c r="BQ27" t="inlineStr"/>
-      <c r="BR27" t="inlineStr"/>
-      <c r="BS27" t="inlineStr"/>
-      <c r="BT27" t="inlineStr"/>
-      <c r="BU27" t="inlineStr"/>
-      <c r="BV27" t="inlineStr"/>
-      <c r="BW27" t="inlineStr"/>
-      <c r="BX27" t="inlineStr"/>
       <c r="BY27" t="inlineStr">
         <is>
           <t>State Pension Co-Invest</t>
@@ -9661,30 +8265,11 @@
       <c r="CA27" t="n">
         <v>189250205</v>
       </c>
-      <c r="CB27" t="inlineStr"/>
-      <c r="CC27" t="inlineStr"/>
-      <c r="CD27" t="inlineStr"/>
-      <c r="CE27" t="inlineStr"/>
       <c r="CF27" t="inlineStr">
         <is>
           <t>Cub Foods (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG27" t="inlineStr"/>
-      <c r="CH27" t="inlineStr"/>
-      <c r="CI27" t="inlineStr"/>
-      <c r="CJ27" t="inlineStr"/>
-      <c r="CK27" t="inlineStr"/>
-      <c r="CL27" t="inlineStr"/>
-      <c r="CM27" t="inlineStr"/>
-      <c r="CN27" t="inlineStr"/>
-      <c r="CO27" t="inlineStr"/>
-      <c r="CP27" t="inlineStr"/>
-      <c r="CQ27" t="inlineStr"/>
-      <c r="CR27" t="inlineStr"/>
-      <c r="CS27" t="inlineStr"/>
-      <c r="CT27" t="inlineStr"/>
-      <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="inlineStr">
         <is>
           <t>Neighborhood</t>
@@ -9717,22 +8302,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD27" t="inlineStr"/>
-      <c r="DE27" t="inlineStr"/>
-      <c r="DF27" t="inlineStr"/>
-      <c r="DG27" t="inlineStr"/>
-      <c r="DH27" t="inlineStr"/>
-      <c r="DI27" t="inlineStr"/>
-      <c r="DJ27" t="inlineStr"/>
-      <c r="DK27" t="inlineStr"/>
-      <c r="DL27" t="inlineStr"/>
-      <c r="DM27" t="inlineStr"/>
-      <c r="DN27" t="inlineStr"/>
-      <c r="DO27" t="inlineStr"/>
-      <c r="DP27" t="inlineStr"/>
-      <c r="DQ27" t="inlineStr"/>
-      <c r="DR27" t="inlineStr"/>
-      <c r="DS27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9786,7 +8355,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -9811,7 +8379,6 @@
       <c r="R28" t="n">
         <v>1999</v>
       </c>
-      <c r="S28" t="inlineStr"/>
       <c r="T28" t="n">
         <v>1</v>
       </c>
@@ -9826,7 +8393,6 @@
           <t>NNN</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
         <v>156000000</v>
       </c>
@@ -9854,7 +8420,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -9872,15 +8437,6 @@
       <c r="AK28" t="n">
         <v>1</v>
       </c>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
       <c r="AU28" t="inlineStr">
         <is>
           <t>Capitol City Assets</t>
@@ -9995,23 +8551,12 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="n">
         <v>100</v>
       </c>
       <c r="CA28" t="n">
         <v>180879838</v>
       </c>
-      <c r="CB28" t="inlineStr"/>
-      <c r="CC28" t="inlineStr"/>
-      <c r="CD28" t="inlineStr"/>
-      <c r="CE28" t="inlineStr"/>
-      <c r="CF28" t="inlineStr"/>
-      <c r="CG28" t="inlineStr"/>
-      <c r="CH28" t="inlineStr"/>
-      <c r="CI28" t="inlineStr"/>
-      <c r="CJ28" t="inlineStr"/>
-      <c r="CK28" t="inlineStr"/>
       <c r="CL28" t="n">
         <v>24</v>
       </c>
@@ -10048,30 +8593,6 @@
       <c r="CU28" t="n">
         <v>185</v>
       </c>
-      <c r="CV28" t="inlineStr"/>
-      <c r="CW28" t="inlineStr"/>
-      <c r="CX28" t="inlineStr"/>
-      <c r="CY28" t="inlineStr"/>
-      <c r="CZ28" t="inlineStr"/>
-      <c r="DA28" t="inlineStr"/>
-      <c r="DB28" t="inlineStr"/>
-      <c r="DC28" t="inlineStr"/>
-      <c r="DD28" t="inlineStr"/>
-      <c r="DE28" t="inlineStr"/>
-      <c r="DF28" t="inlineStr"/>
-      <c r="DG28" t="inlineStr"/>
-      <c r="DH28" t="inlineStr"/>
-      <c r="DI28" t="inlineStr"/>
-      <c r="DJ28" t="inlineStr"/>
-      <c r="DK28" t="inlineStr"/>
-      <c r="DL28" t="inlineStr"/>
-      <c r="DM28" t="inlineStr"/>
-      <c r="DN28" t="inlineStr"/>
-      <c r="DO28" t="inlineStr"/>
-      <c r="DP28" t="inlineStr"/>
-      <c r="DQ28" t="inlineStr"/>
-      <c r="DR28" t="inlineStr"/>
-      <c r="DS28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10125,7 +8646,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -10167,7 +8687,6 @@
           <t>Gross</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
         <v>294000000</v>
       </c>
@@ -10195,7 +8714,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -10213,13 +8731,6 @@
       <c r="AK29" t="n">
         <v>14</v>
       </c>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
       <c r="AS29" t="n">
         <v>4350000</v>
       </c>
@@ -10395,40 +8906,6 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="CL29" t="inlineStr"/>
-      <c r="CM29" t="inlineStr"/>
-      <c r="CN29" t="inlineStr"/>
-      <c r="CO29" t="inlineStr"/>
-      <c r="CP29" t="inlineStr"/>
-      <c r="CQ29" t="inlineStr"/>
-      <c r="CR29" t="inlineStr"/>
-      <c r="CS29" t="inlineStr"/>
-      <c r="CT29" t="inlineStr"/>
-      <c r="CU29" t="inlineStr"/>
-      <c r="CV29" t="inlineStr"/>
-      <c r="CW29" t="inlineStr"/>
-      <c r="CX29" t="inlineStr"/>
-      <c r="CY29" t="inlineStr"/>
-      <c r="CZ29" t="inlineStr"/>
-      <c r="DA29" t="inlineStr"/>
-      <c r="DB29" t="inlineStr"/>
-      <c r="DC29" t="inlineStr"/>
-      <c r="DD29" t="inlineStr"/>
-      <c r="DE29" t="inlineStr"/>
-      <c r="DF29" t="inlineStr"/>
-      <c r="DG29" t="inlineStr"/>
-      <c r="DH29" t="inlineStr"/>
-      <c r="DI29" t="inlineStr"/>
-      <c r="DJ29" t="inlineStr"/>
-      <c r="DK29" t="inlineStr"/>
-      <c r="DL29" t="inlineStr"/>
-      <c r="DM29" t="inlineStr"/>
-      <c r="DN29" t="inlineStr"/>
-      <c r="DO29" t="inlineStr"/>
-      <c r="DP29" t="inlineStr"/>
-      <c r="DQ29" t="inlineStr"/>
-      <c r="DR29" t="inlineStr"/>
-      <c r="DS29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10482,11 +8959,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>I-494 Corridor</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -10511,7 +8983,6 @@
       <c r="R30" t="n">
         <v>1980</v>
       </c>
-      <c r="S30" t="inlineStr"/>
       <c r="T30" t="n">
         <v>1</v>
       </c>
@@ -10556,7 +9027,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -10574,15 +9044,6 @@
       <c r="AK30" t="n">
         <v>1</v>
       </c>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
       <c r="AU30" t="inlineStr">
         <is>
           <t>SouthPoint Advisors</t>
@@ -10593,11 +9054,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
-      <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="n">
         <v>7</v>
       </c>
@@ -10643,47 +9099,17 @@
       <c r="BN30" t="n">
         <v>1.08</v>
       </c>
-      <c r="BO30" t="inlineStr"/>
-      <c r="BP30" t="inlineStr"/>
-      <c r="BQ30" t="inlineStr"/>
-      <c r="BR30" t="inlineStr"/>
-      <c r="BS30" t="inlineStr"/>
-      <c r="BT30" t="inlineStr"/>
-      <c r="BU30" t="inlineStr"/>
-      <c r="BV30" t="inlineStr"/>
-      <c r="BW30" t="inlineStr"/>
-      <c r="BX30" t="inlineStr"/>
-      <c r="BY30" t="inlineStr"/>
       <c r="BZ30" t="n">
         <v>100</v>
       </c>
       <c r="CA30" t="n">
         <v>336952118</v>
       </c>
-      <c r="CB30" t="inlineStr"/>
-      <c r="CC30" t="inlineStr"/>
-      <c r="CD30" t="inlineStr"/>
-      <c r="CE30" t="inlineStr"/>
       <c r="CF30" t="inlineStr">
         <is>
           <t>Cub Foods (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG30" t="inlineStr"/>
-      <c r="CH30" t="inlineStr"/>
-      <c r="CI30" t="inlineStr"/>
-      <c r="CJ30" t="inlineStr"/>
-      <c r="CK30" t="inlineStr"/>
-      <c r="CL30" t="inlineStr"/>
-      <c r="CM30" t="inlineStr"/>
-      <c r="CN30" t="inlineStr"/>
-      <c r="CO30" t="inlineStr"/>
-      <c r="CP30" t="inlineStr"/>
-      <c r="CQ30" t="inlineStr"/>
-      <c r="CR30" t="inlineStr"/>
-      <c r="CS30" t="inlineStr"/>
-      <c r="CT30" t="inlineStr"/>
-      <c r="CU30" t="inlineStr"/>
       <c r="CV30" t="inlineStr">
         <is>
           <t>Lifestyle</t>
@@ -10716,22 +9142,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD30" t="inlineStr"/>
-      <c r="DE30" t="inlineStr"/>
-      <c r="DF30" t="inlineStr"/>
-      <c r="DG30" t="inlineStr"/>
-      <c r="DH30" t="inlineStr"/>
-      <c r="DI30" t="inlineStr"/>
-      <c r="DJ30" t="inlineStr"/>
-      <c r="DK30" t="inlineStr"/>
-      <c r="DL30" t="inlineStr"/>
-      <c r="DM30" t="inlineStr"/>
-      <c r="DN30" t="inlineStr"/>
-      <c r="DO30" t="inlineStr"/>
-      <c r="DP30" t="inlineStr"/>
-      <c r="DQ30" t="inlineStr"/>
-      <c r="DR30" t="inlineStr"/>
-      <c r="DS30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10780,30 +9190,19 @@
           <t>Land</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Existing</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>Institutional</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
         <v>282000000</v>
       </c>
@@ -10812,9 +9211,6 @@
           <t>2022-09-13</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
           <t>MX-2</t>
@@ -10825,25 +9221,11 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr">
         <is>
           <t>North Fund IV</t>
@@ -10854,82 +9236,15 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr"/>
-      <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="inlineStr"/>
-      <c r="BF31" t="inlineStr"/>
-      <c r="BG31" t="inlineStr"/>
-      <c r="BH31" t="inlineStr"/>
-      <c r="BI31" t="inlineStr"/>
-      <c r="BJ31" t="inlineStr"/>
-      <c r="BK31" t="inlineStr"/>
-      <c r="BL31" t="inlineStr"/>
-      <c r="BM31" t="inlineStr"/>
-      <c r="BN31" t="inlineStr"/>
-      <c r="BO31" t="inlineStr"/>
-      <c r="BP31" t="inlineStr"/>
-      <c r="BQ31" t="inlineStr"/>
-      <c r="BR31" t="inlineStr"/>
-      <c r="BS31" t="inlineStr"/>
-      <c r="BT31" t="inlineStr"/>
-      <c r="BU31" t="inlineStr"/>
-      <c r="BV31" t="inlineStr"/>
-      <c r="BW31" t="inlineStr"/>
-      <c r="BX31" t="inlineStr"/>
-      <c r="BY31" t="inlineStr"/>
       <c r="BZ31" t="n">
         <v>100</v>
       </c>
       <c r="CA31" t="n">
         <v>301433305</v>
       </c>
-      <c r="CB31" t="inlineStr"/>
-      <c r="CC31" t="inlineStr"/>
-      <c r="CD31" t="inlineStr"/>
-      <c r="CE31" t="inlineStr"/>
-      <c r="CF31" t="inlineStr"/>
-      <c r="CG31" t="inlineStr"/>
-      <c r="CH31" t="inlineStr"/>
-      <c r="CI31" t="inlineStr"/>
-      <c r="CJ31" t="inlineStr"/>
-      <c r="CK31" t="inlineStr"/>
-      <c r="CL31" t="inlineStr"/>
-      <c r="CM31" t="inlineStr"/>
-      <c r="CN31" t="inlineStr"/>
-      <c r="CO31" t="inlineStr"/>
-      <c r="CP31" t="inlineStr"/>
-      <c r="CQ31" t="inlineStr"/>
-      <c r="CR31" t="inlineStr"/>
-      <c r="CS31" t="inlineStr"/>
-      <c r="CT31" t="inlineStr"/>
-      <c r="CU31" t="inlineStr"/>
-      <c r="CV31" t="inlineStr"/>
-      <c r="CW31" t="inlineStr"/>
       <c r="CX31" t="n">
         <v>1425</v>
       </c>
-      <c r="CY31" t="inlineStr"/>
-      <c r="CZ31" t="inlineStr"/>
-      <c r="DA31" t="inlineStr"/>
-      <c r="DB31" t="inlineStr"/>
-      <c r="DC31" t="inlineStr"/>
-      <c r="DD31" t="inlineStr"/>
-      <c r="DE31" t="inlineStr"/>
-      <c r="DF31" t="inlineStr"/>
-      <c r="DG31" t="inlineStr"/>
-      <c r="DH31" t="inlineStr"/>
-      <c r="DI31" t="inlineStr"/>
-      <c r="DJ31" t="inlineStr"/>
-      <c r="DK31" t="inlineStr"/>
-      <c r="DL31" t="inlineStr"/>
-      <c r="DM31" t="inlineStr"/>
-      <c r="DN31" t="inlineStr"/>
       <c r="DO31" t="inlineStr">
         <is>
           <t>No</t>
@@ -11008,7 +9323,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -11033,7 +9347,6 @@
       <c r="R32" t="n">
         <v>1969</v>
       </c>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="n">
         <v>4</v>
       </c>
@@ -11051,9 +9364,6 @@
       <c r="X32" t="n">
         <v>8.15</v>
       </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="n">
         <v>804</v>
       </c>
@@ -11070,7 +9380,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -11104,13 +9413,6 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
           <t>Great Lakes Life Co.</t>
@@ -11147,8 +9449,6 @@
           <t>2 x 5yr</t>
         </is>
       </c>
-      <c r="BG32" t="inlineStr"/>
-      <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr">
         <is>
           <t>2027-09</t>
@@ -11217,35 +9517,6 @@
       <c r="BZ32" t="n">
         <v>50</v>
       </c>
-      <c r="CA32" t="inlineStr"/>
-      <c r="CB32" t="inlineStr"/>
-      <c r="CC32" t="inlineStr"/>
-      <c r="CD32" t="inlineStr"/>
-      <c r="CE32" t="inlineStr"/>
-      <c r="CF32" t="inlineStr"/>
-      <c r="CG32" t="inlineStr"/>
-      <c r="CH32" t="inlineStr"/>
-      <c r="CI32" t="inlineStr"/>
-      <c r="CJ32" t="inlineStr"/>
-      <c r="CK32" t="inlineStr"/>
-      <c r="CL32" t="inlineStr"/>
-      <c r="CM32" t="inlineStr"/>
-      <c r="CN32" t="inlineStr"/>
-      <c r="CO32" t="inlineStr"/>
-      <c r="CP32" t="inlineStr"/>
-      <c r="CQ32" t="inlineStr"/>
-      <c r="CR32" t="inlineStr"/>
-      <c r="CS32" t="inlineStr"/>
-      <c r="CT32" t="inlineStr"/>
-      <c r="CU32" t="inlineStr"/>
-      <c r="CV32" t="inlineStr"/>
-      <c r="CW32" t="inlineStr"/>
-      <c r="CX32" t="inlineStr"/>
-      <c r="CY32" t="inlineStr"/>
-      <c r="CZ32" t="inlineStr"/>
-      <c r="DA32" t="inlineStr"/>
-      <c r="DB32" t="inlineStr"/>
-      <c r="DC32" t="inlineStr"/>
       <c r="DD32" t="n">
         <v>362</v>
       </c>
@@ -11287,11 +9558,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO32" t="inlineStr"/>
-      <c r="DP32" t="inlineStr"/>
-      <c r="DQ32" t="inlineStr"/>
-      <c r="DR32" t="inlineStr"/>
-      <c r="DS32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11345,7 +9611,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -11370,7 +9635,6 @@
       <c r="R33" t="n">
         <v>2002</v>
       </c>
-      <c r="S33" t="inlineStr"/>
       <c r="T33" t="n">
         <v>12</v>
       </c>
@@ -11415,7 +9679,6 @@
           <t>Gateway Industrial REIT</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -11449,11 +9712,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
       <c r="AU33" t="inlineStr">
         <is>
           <t>Gateway Industrial REIT</t>
@@ -11500,8 +9758,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="BG33" t="inlineStr"/>
-      <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
           <t>2026-01</t>
@@ -11562,41 +9818,12 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="BY33" t="inlineStr"/>
       <c r="BZ33" t="n">
         <v>100</v>
       </c>
       <c r="CA33" t="n">
         <v>172967506</v>
       </c>
-      <c r="CB33" t="inlineStr"/>
-      <c r="CC33" t="inlineStr"/>
-      <c r="CD33" t="inlineStr"/>
-      <c r="CE33" t="inlineStr"/>
-      <c r="CF33" t="inlineStr"/>
-      <c r="CG33" t="inlineStr"/>
-      <c r="CH33" t="inlineStr"/>
-      <c r="CI33" t="inlineStr"/>
-      <c r="CJ33" t="inlineStr"/>
-      <c r="CK33" t="inlineStr"/>
-      <c r="CL33" t="inlineStr"/>
-      <c r="CM33" t="inlineStr"/>
-      <c r="CN33" t="inlineStr"/>
-      <c r="CO33" t="inlineStr"/>
-      <c r="CP33" t="inlineStr"/>
-      <c r="CQ33" t="inlineStr"/>
-      <c r="CR33" t="inlineStr"/>
-      <c r="CS33" t="inlineStr"/>
-      <c r="CT33" t="inlineStr"/>
-      <c r="CU33" t="inlineStr"/>
-      <c r="CV33" t="inlineStr"/>
-      <c r="CW33" t="inlineStr"/>
-      <c r="CX33" t="inlineStr"/>
-      <c r="CY33" t="inlineStr"/>
-      <c r="CZ33" t="inlineStr"/>
-      <c r="DA33" t="inlineStr"/>
-      <c r="DB33" t="inlineStr"/>
-      <c r="DC33" t="inlineStr"/>
       <c r="DD33" t="n">
         <v>278</v>
       </c>
@@ -11638,11 +9865,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO33" t="inlineStr"/>
-      <c r="DP33" t="inlineStr"/>
-      <c r="DQ33" t="inlineStr"/>
-      <c r="DR33" t="inlineStr"/>
-      <c r="DS33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11696,7 +9918,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -11721,7 +9942,6 @@
       <c r="R34" t="n">
         <v>2024</v>
       </c>
-      <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
         <v>35</v>
       </c>
@@ -11766,7 +9986,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -11784,15 +10003,6 @@
       <c r="AK34" t="n">
         <v>23</v>
       </c>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
       <c r="AU34" t="inlineStr">
         <is>
           <t>North Fund IV</t>
@@ -11803,11 +10013,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="n">
         <v>11.3</v>
       </c>
@@ -11853,17 +10058,6 @@
       <c r="BN34" t="n">
         <v>0.35</v>
       </c>
-      <c r="BO34" t="inlineStr"/>
-      <c r="BP34" t="inlineStr"/>
-      <c r="BQ34" t="inlineStr"/>
-      <c r="BR34" t="inlineStr"/>
-      <c r="BS34" t="inlineStr"/>
-      <c r="BT34" t="inlineStr"/>
-      <c r="BU34" t="inlineStr"/>
-      <c r="BV34" t="inlineStr"/>
-      <c r="BW34" t="inlineStr"/>
-      <c r="BX34" t="inlineStr"/>
-      <c r="BY34" t="inlineStr"/>
       <c r="BZ34" t="n">
         <v>100</v>
       </c>
@@ -11912,40 +10106,6 @@
           <t>Structured</t>
         </is>
       </c>
-      <c r="CL34" t="inlineStr"/>
-      <c r="CM34" t="inlineStr"/>
-      <c r="CN34" t="inlineStr"/>
-      <c r="CO34" t="inlineStr"/>
-      <c r="CP34" t="inlineStr"/>
-      <c r="CQ34" t="inlineStr"/>
-      <c r="CR34" t="inlineStr"/>
-      <c r="CS34" t="inlineStr"/>
-      <c r="CT34" t="inlineStr"/>
-      <c r="CU34" t="inlineStr"/>
-      <c r="CV34" t="inlineStr"/>
-      <c r="CW34" t="inlineStr"/>
-      <c r="CX34" t="inlineStr"/>
-      <c r="CY34" t="inlineStr"/>
-      <c r="CZ34" t="inlineStr"/>
-      <c r="DA34" t="inlineStr"/>
-      <c r="DB34" t="inlineStr"/>
-      <c r="DC34" t="inlineStr"/>
-      <c r="DD34" t="inlineStr"/>
-      <c r="DE34" t="inlineStr"/>
-      <c r="DF34" t="inlineStr"/>
-      <c r="DG34" t="inlineStr"/>
-      <c r="DH34" t="inlineStr"/>
-      <c r="DI34" t="inlineStr"/>
-      <c r="DJ34" t="inlineStr"/>
-      <c r="DK34" t="inlineStr"/>
-      <c r="DL34" t="inlineStr"/>
-      <c r="DM34" t="inlineStr"/>
-      <c r="DN34" t="inlineStr"/>
-      <c r="DO34" t="inlineStr"/>
-      <c r="DP34" t="inlineStr"/>
-      <c r="DQ34" t="inlineStr"/>
-      <c r="DR34" t="inlineStr"/>
-      <c r="DS34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11999,7 +10159,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -12071,7 +10230,6 @@
           <t>Twin Cities Ventures</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -12105,9 +10263,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="n">
         <v>9850000</v>
       </c>
@@ -12195,8 +10350,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP35" t="inlineStr"/>
-      <c r="BQ35" t="inlineStr"/>
       <c r="BR35" t="n">
         <v>25</v>
       </c>
@@ -12224,7 +10377,6 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="n">
         <v>100</v>
       </c>
@@ -12273,40 +10425,6 @@
           <t>Underground</t>
         </is>
       </c>
-      <c r="CL35" t="inlineStr"/>
-      <c r="CM35" t="inlineStr"/>
-      <c r="CN35" t="inlineStr"/>
-      <c r="CO35" t="inlineStr"/>
-      <c r="CP35" t="inlineStr"/>
-      <c r="CQ35" t="inlineStr"/>
-      <c r="CR35" t="inlineStr"/>
-      <c r="CS35" t="inlineStr"/>
-      <c r="CT35" t="inlineStr"/>
-      <c r="CU35" t="inlineStr"/>
-      <c r="CV35" t="inlineStr"/>
-      <c r="CW35" t="inlineStr"/>
-      <c r="CX35" t="inlineStr"/>
-      <c r="CY35" t="inlineStr"/>
-      <c r="CZ35" t="inlineStr"/>
-      <c r="DA35" t="inlineStr"/>
-      <c r="DB35" t="inlineStr"/>
-      <c r="DC35" t="inlineStr"/>
-      <c r="DD35" t="inlineStr"/>
-      <c r="DE35" t="inlineStr"/>
-      <c r="DF35" t="inlineStr"/>
-      <c r="DG35" t="inlineStr"/>
-      <c r="DH35" t="inlineStr"/>
-      <c r="DI35" t="inlineStr"/>
-      <c r="DJ35" t="inlineStr"/>
-      <c r="DK35" t="inlineStr"/>
-      <c r="DL35" t="inlineStr"/>
-      <c r="DM35" t="inlineStr"/>
-      <c r="DN35" t="inlineStr"/>
-      <c r="DO35" t="inlineStr"/>
-      <c r="DP35" t="inlineStr"/>
-      <c r="DQ35" t="inlineStr"/>
-      <c r="DR35" t="inlineStr"/>
-      <c r="DS35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12355,35 +10473,19 @@
           <t>Land</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Existing</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>REIT</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
         <v>7.2</v>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr">
         <is>
           <t>MX-2</t>
@@ -12394,101 +10496,17 @@
           <t>Heartland REIT</t>
         </is>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
         </is>
       </c>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="inlineStr"/>
-      <c r="BG36" t="inlineStr"/>
-      <c r="BH36" t="inlineStr"/>
-      <c r="BI36" t="inlineStr"/>
-      <c r="BJ36" t="inlineStr"/>
-      <c r="BK36" t="inlineStr"/>
-      <c r="BL36" t="inlineStr"/>
-      <c r="BM36" t="inlineStr"/>
-      <c r="BN36" t="inlineStr"/>
-      <c r="BO36" t="inlineStr"/>
-      <c r="BP36" t="inlineStr"/>
-      <c r="BQ36" t="inlineStr"/>
-      <c r="BR36" t="inlineStr"/>
-      <c r="BS36" t="inlineStr"/>
-      <c r="BT36" t="inlineStr"/>
-      <c r="BU36" t="inlineStr"/>
-      <c r="BV36" t="inlineStr"/>
-      <c r="BW36" t="inlineStr"/>
-      <c r="BX36" t="inlineStr"/>
-      <c r="BY36" t="inlineStr"/>
       <c r="BZ36" t="n">
         <v>100</v>
       </c>
-      <c r="CA36" t="inlineStr"/>
-      <c r="CB36" t="inlineStr"/>
-      <c r="CC36" t="inlineStr"/>
-      <c r="CD36" t="inlineStr"/>
-      <c r="CE36" t="inlineStr"/>
-      <c r="CF36" t="inlineStr"/>
-      <c r="CG36" t="inlineStr"/>
-      <c r="CH36" t="inlineStr"/>
-      <c r="CI36" t="inlineStr"/>
-      <c r="CJ36" t="inlineStr"/>
-      <c r="CK36" t="inlineStr"/>
-      <c r="CL36" t="inlineStr"/>
-      <c r="CM36" t="inlineStr"/>
-      <c r="CN36" t="inlineStr"/>
-      <c r="CO36" t="inlineStr"/>
-      <c r="CP36" t="inlineStr"/>
-      <c r="CQ36" t="inlineStr"/>
-      <c r="CR36" t="inlineStr"/>
-      <c r="CS36" t="inlineStr"/>
-      <c r="CT36" t="inlineStr"/>
-      <c r="CU36" t="inlineStr"/>
-      <c r="CV36" t="inlineStr"/>
-      <c r="CW36" t="inlineStr"/>
       <c r="CX36" t="n">
         <v>1050</v>
       </c>
-      <c r="CY36" t="inlineStr"/>
-      <c r="CZ36" t="inlineStr"/>
-      <c r="DA36" t="inlineStr"/>
-      <c r="DB36" t="inlineStr"/>
-      <c r="DC36" t="inlineStr"/>
-      <c r="DD36" t="inlineStr"/>
-      <c r="DE36" t="inlineStr"/>
-      <c r="DF36" t="inlineStr"/>
-      <c r="DG36" t="inlineStr"/>
-      <c r="DH36" t="inlineStr"/>
-      <c r="DI36" t="inlineStr"/>
-      <c r="DJ36" t="inlineStr"/>
-      <c r="DK36" t="inlineStr"/>
-      <c r="DL36" t="inlineStr"/>
-      <c r="DM36" t="inlineStr"/>
-      <c r="DN36" t="inlineStr"/>
       <c r="DO36" t="inlineStr">
         <is>
           <t>No</t>
@@ -12567,7 +10585,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -12639,7 +10656,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -12673,9 +10689,6 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="n">
         <v>9675000</v>
       </c>
@@ -12730,8 +10743,6 @@
           <t>2 x 5yr</t>
         </is>
       </c>
-      <c r="BG37" t="inlineStr"/>
-      <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
         <is>
           <t>2033-04</t>
@@ -12757,8 +10768,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP37" t="inlineStr"/>
-      <c r="BQ37" t="inlineStr"/>
       <c r="BR37" t="n">
         <v>30</v>
       </c>
@@ -12797,34 +10806,6 @@
       <c r="CA37" t="n">
         <v>90494629</v>
       </c>
-      <c r="CB37" t="inlineStr"/>
-      <c r="CC37" t="inlineStr"/>
-      <c r="CD37" t="inlineStr"/>
-      <c r="CE37" t="inlineStr"/>
-      <c r="CF37" t="inlineStr"/>
-      <c r="CG37" t="inlineStr"/>
-      <c r="CH37" t="inlineStr"/>
-      <c r="CI37" t="inlineStr"/>
-      <c r="CJ37" t="inlineStr"/>
-      <c r="CK37" t="inlineStr"/>
-      <c r="CL37" t="inlineStr"/>
-      <c r="CM37" t="inlineStr"/>
-      <c r="CN37" t="inlineStr"/>
-      <c r="CO37" t="inlineStr"/>
-      <c r="CP37" t="inlineStr"/>
-      <c r="CQ37" t="inlineStr"/>
-      <c r="CR37" t="inlineStr"/>
-      <c r="CS37" t="inlineStr"/>
-      <c r="CT37" t="inlineStr"/>
-      <c r="CU37" t="inlineStr"/>
-      <c r="CV37" t="inlineStr"/>
-      <c r="CW37" t="inlineStr"/>
-      <c r="CX37" t="inlineStr"/>
-      <c r="CY37" t="inlineStr"/>
-      <c r="CZ37" t="inlineStr"/>
-      <c r="DA37" t="inlineStr"/>
-      <c r="DB37" t="inlineStr"/>
-      <c r="DC37" t="inlineStr"/>
       <c r="DD37" t="n">
         <v>500</v>
       </c>
@@ -12866,11 +10847,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO37" t="inlineStr"/>
-      <c r="DP37" t="inlineStr"/>
-      <c r="DQ37" t="inlineStr"/>
-      <c r="DR37" t="inlineStr"/>
-      <c r="DS37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12924,7 +10900,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -12949,7 +10924,6 @@
       <c r="R38" t="n">
         <v>2013</v>
       </c>
-      <c r="S38" t="inlineStr"/>
       <c r="T38" t="n">
         <v>1</v>
       </c>
@@ -12994,7 +10968,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -13028,11 +11001,6 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
       <c r="AU38" t="inlineStr">
         <is>
           <t>Capitol City Assets</t>
@@ -13147,23 +11115,12 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="BY38" t="inlineStr"/>
       <c r="BZ38" t="n">
         <v>100</v>
       </c>
       <c r="CA38" t="n">
         <v>284772666</v>
       </c>
-      <c r="CB38" t="inlineStr"/>
-      <c r="CC38" t="inlineStr"/>
-      <c r="CD38" t="inlineStr"/>
-      <c r="CE38" t="inlineStr"/>
-      <c r="CF38" t="inlineStr"/>
-      <c r="CG38" t="inlineStr"/>
-      <c r="CH38" t="inlineStr"/>
-      <c r="CI38" t="inlineStr"/>
-      <c r="CJ38" t="inlineStr"/>
-      <c r="CK38" t="inlineStr"/>
       <c r="CL38" t="n">
         <v>28</v>
       </c>
@@ -13200,30 +11157,6 @@
       <c r="CU38" t="n">
         <v>135</v>
       </c>
-      <c r="CV38" t="inlineStr"/>
-      <c r="CW38" t="inlineStr"/>
-      <c r="CX38" t="inlineStr"/>
-      <c r="CY38" t="inlineStr"/>
-      <c r="CZ38" t="inlineStr"/>
-      <c r="DA38" t="inlineStr"/>
-      <c r="DB38" t="inlineStr"/>
-      <c r="DC38" t="inlineStr"/>
-      <c r="DD38" t="inlineStr"/>
-      <c r="DE38" t="inlineStr"/>
-      <c r="DF38" t="inlineStr"/>
-      <c r="DG38" t="inlineStr"/>
-      <c r="DH38" t="inlineStr"/>
-      <c r="DI38" t="inlineStr"/>
-      <c r="DJ38" t="inlineStr"/>
-      <c r="DK38" t="inlineStr"/>
-      <c r="DL38" t="inlineStr"/>
-      <c r="DM38" t="inlineStr"/>
-      <c r="DN38" t="inlineStr"/>
-      <c r="DO38" t="inlineStr"/>
-      <c r="DP38" t="inlineStr"/>
-      <c r="DQ38" t="inlineStr"/>
-      <c r="DR38" t="inlineStr"/>
-      <c r="DS38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13277,7 +11210,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -13302,7 +11234,6 @@
       <c r="R39" t="n">
         <v>1940</v>
       </c>
-      <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
         <v>20</v>
       </c>
@@ -13317,7 +11248,6 @@
           <t>Gross</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
         <v>130000000</v>
       </c>
@@ -13345,7 +11275,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -13363,15 +11292,6 @@
       <c r="AK39" t="n">
         <v>39</v>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
       <c r="AU39" t="inlineStr">
         <is>
           <t>Mall Street Partners</t>
@@ -13418,8 +11338,6 @@
           <t>1 x 10yr</t>
         </is>
       </c>
-      <c r="BG39" t="inlineStr"/>
-      <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr">
         <is>
           <t>2026-05</t>
@@ -13445,8 +11363,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP39" t="inlineStr"/>
-      <c r="BQ39" t="inlineStr"/>
       <c r="BR39" t="n">
         <v>30</v>
       </c>
@@ -13485,34 +11401,6 @@
       <c r="CA39" t="n">
         <v>156925658</v>
       </c>
-      <c r="CB39" t="inlineStr"/>
-      <c r="CC39" t="inlineStr"/>
-      <c r="CD39" t="inlineStr"/>
-      <c r="CE39" t="inlineStr"/>
-      <c r="CF39" t="inlineStr"/>
-      <c r="CG39" t="inlineStr"/>
-      <c r="CH39" t="inlineStr"/>
-      <c r="CI39" t="inlineStr"/>
-      <c r="CJ39" t="inlineStr"/>
-      <c r="CK39" t="inlineStr"/>
-      <c r="CL39" t="inlineStr"/>
-      <c r="CM39" t="inlineStr"/>
-      <c r="CN39" t="inlineStr"/>
-      <c r="CO39" t="inlineStr"/>
-      <c r="CP39" t="inlineStr"/>
-      <c r="CQ39" t="inlineStr"/>
-      <c r="CR39" t="inlineStr"/>
-      <c r="CS39" t="inlineStr"/>
-      <c r="CT39" t="inlineStr"/>
-      <c r="CU39" t="inlineStr"/>
-      <c r="CV39" t="inlineStr"/>
-      <c r="CW39" t="inlineStr"/>
-      <c r="CX39" t="inlineStr"/>
-      <c r="CY39" t="inlineStr"/>
-      <c r="CZ39" t="inlineStr"/>
-      <c r="DA39" t="inlineStr"/>
-      <c r="DB39" t="inlineStr"/>
-      <c r="DC39" t="inlineStr"/>
       <c r="DD39" t="n">
         <v>311</v>
       </c>
@@ -13554,11 +11442,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO39" t="inlineStr"/>
-      <c r="DP39" t="inlineStr"/>
-      <c r="DQ39" t="inlineStr"/>
-      <c r="DR39" t="inlineStr"/>
-      <c r="DS39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -13612,7 +11495,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -13637,7 +11519,6 @@
       <c r="R40" t="n">
         <v>2020</v>
       </c>
-      <c r="S40" t="inlineStr"/>
       <c r="T40" t="n">
         <v>1</v>
       </c>
@@ -13682,7 +11563,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -13716,11 +11596,6 @@
           <t>Complete</t>
         </is>
       </c>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr"/>
-      <c r="AS40" t="inlineStr"/>
-      <c r="AT40" t="inlineStr"/>
       <c r="AU40" t="inlineStr">
         <is>
           <t>SouthPoint Advisors</t>
@@ -13800,8 +11675,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP40" t="inlineStr"/>
-      <c r="BQ40" t="inlineStr"/>
       <c r="BR40" t="n">
         <v>30</v>
       </c>
@@ -13840,16 +11713,6 @@
       <c r="CA40" t="n">
         <v>33115343</v>
       </c>
-      <c r="CB40" t="inlineStr"/>
-      <c r="CC40" t="inlineStr"/>
-      <c r="CD40" t="inlineStr"/>
-      <c r="CE40" t="inlineStr"/>
-      <c r="CF40" t="inlineStr"/>
-      <c r="CG40" t="inlineStr"/>
-      <c r="CH40" t="inlineStr"/>
-      <c r="CI40" t="inlineStr"/>
-      <c r="CJ40" t="inlineStr"/>
-      <c r="CK40" t="inlineStr"/>
       <c r="CL40" t="n">
         <v>24</v>
       </c>
@@ -13886,30 +11749,6 @@
       <c r="CU40" t="n">
         <v>110</v>
       </c>
-      <c r="CV40" t="inlineStr"/>
-      <c r="CW40" t="inlineStr"/>
-      <c r="CX40" t="inlineStr"/>
-      <c r="CY40" t="inlineStr"/>
-      <c r="CZ40" t="inlineStr"/>
-      <c r="DA40" t="inlineStr"/>
-      <c r="DB40" t="inlineStr"/>
-      <c r="DC40" t="inlineStr"/>
-      <c r="DD40" t="inlineStr"/>
-      <c r="DE40" t="inlineStr"/>
-      <c r="DF40" t="inlineStr"/>
-      <c r="DG40" t="inlineStr"/>
-      <c r="DH40" t="inlineStr"/>
-      <c r="DI40" t="inlineStr"/>
-      <c r="DJ40" t="inlineStr"/>
-      <c r="DK40" t="inlineStr"/>
-      <c r="DL40" t="inlineStr"/>
-      <c r="DM40" t="inlineStr"/>
-      <c r="DN40" t="inlineStr"/>
-      <c r="DO40" t="inlineStr"/>
-      <c r="DP40" t="inlineStr"/>
-      <c r="DQ40" t="inlineStr"/>
-      <c r="DR40" t="inlineStr"/>
-      <c r="DS40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13963,7 +11802,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -13988,7 +11826,6 @@
       <c r="R41" t="n">
         <v>1992</v>
       </c>
-      <c r="S41" t="inlineStr"/>
       <c r="T41" t="n">
         <v>14</v>
       </c>
@@ -14033,7 +11870,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -14082,8 +11918,6 @@
           <t>2028-Q1</t>
         </is>
       </c>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
       <c r="AU41" t="inlineStr">
         <is>
           <t>SouthPoint Advisors</t>
@@ -14094,11 +11928,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
-      <c r="BA41" t="inlineStr"/>
       <c r="BB41" t="n">
         <v>4.2</v>
       </c>
@@ -14116,8 +11945,6 @@
           <t>1 x 5yr</t>
         </is>
       </c>
-      <c r="BG41" t="inlineStr"/>
-      <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr">
         <is>
           <t>2033-02</t>
@@ -14138,51 +11965,12 @@
       <c r="BN41" t="n">
         <v>0.25</v>
       </c>
-      <c r="BO41" t="inlineStr"/>
-      <c r="BP41" t="inlineStr"/>
-      <c r="BQ41" t="inlineStr"/>
-      <c r="BR41" t="inlineStr"/>
-      <c r="BS41" t="inlineStr"/>
-      <c r="BT41" t="inlineStr"/>
-      <c r="BU41" t="inlineStr"/>
-      <c r="BV41" t="inlineStr"/>
-      <c r="BW41" t="inlineStr"/>
-      <c r="BX41" t="inlineStr"/>
-      <c r="BY41" t="inlineStr"/>
       <c r="BZ41" t="n">
         <v>100</v>
       </c>
       <c r="CA41" t="n">
         <v>195472859</v>
       </c>
-      <c r="CB41" t="inlineStr"/>
-      <c r="CC41" t="inlineStr"/>
-      <c r="CD41" t="inlineStr"/>
-      <c r="CE41" t="inlineStr"/>
-      <c r="CF41" t="inlineStr"/>
-      <c r="CG41" t="inlineStr"/>
-      <c r="CH41" t="inlineStr"/>
-      <c r="CI41" t="inlineStr"/>
-      <c r="CJ41" t="inlineStr"/>
-      <c r="CK41" t="inlineStr"/>
-      <c r="CL41" t="inlineStr"/>
-      <c r="CM41" t="inlineStr"/>
-      <c r="CN41" t="inlineStr"/>
-      <c r="CO41" t="inlineStr"/>
-      <c r="CP41" t="inlineStr"/>
-      <c r="CQ41" t="inlineStr"/>
-      <c r="CR41" t="inlineStr"/>
-      <c r="CS41" t="inlineStr"/>
-      <c r="CT41" t="inlineStr"/>
-      <c r="CU41" t="inlineStr"/>
-      <c r="CV41" t="inlineStr"/>
-      <c r="CW41" t="inlineStr"/>
-      <c r="CX41" t="inlineStr"/>
-      <c r="CY41" t="inlineStr"/>
-      <c r="CZ41" t="inlineStr"/>
-      <c r="DA41" t="inlineStr"/>
-      <c r="DB41" t="inlineStr"/>
-      <c r="DC41" t="inlineStr"/>
       <c r="DD41" t="n">
         <v>137</v>
       </c>
@@ -14224,11 +12012,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DO41" t="inlineStr"/>
-      <c r="DP41" t="inlineStr"/>
-      <c r="DQ41" t="inlineStr"/>
-      <c r="DR41" t="inlineStr"/>
-      <c r="DS41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14282,7 +12065,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -14307,7 +12089,6 @@
       <c r="R42" t="n">
         <v>1962</v>
       </c>
-      <c r="S42" t="inlineStr"/>
       <c r="T42" t="n">
         <v>6</v>
       </c>
@@ -14352,7 +12133,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -14370,15 +12150,6 @@
       <c r="AK42" t="n">
         <v>9</v>
       </c>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="inlineStr"/>
       <c r="AU42" t="inlineStr">
         <is>
           <t>Capitol City Assets</t>
@@ -14425,8 +12196,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="BG42" t="inlineStr"/>
-      <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr">
         <is>
           <t>2026-01</t>
@@ -14452,8 +12221,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP42" t="inlineStr"/>
-      <c r="BQ42" t="inlineStr"/>
       <c r="BR42" t="n">
         <v>30</v>
       </c>
@@ -14481,41 +12248,12 @@
           <t>2023-02</t>
         </is>
       </c>
-      <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="n">
         <v>100</v>
       </c>
       <c r="CA42" t="n">
         <v>293659778</v>
       </c>
-      <c r="CB42" t="inlineStr"/>
-      <c r="CC42" t="inlineStr"/>
-      <c r="CD42" t="inlineStr"/>
-      <c r="CE42" t="inlineStr"/>
-      <c r="CF42" t="inlineStr"/>
-      <c r="CG42" t="inlineStr"/>
-      <c r="CH42" t="inlineStr"/>
-      <c r="CI42" t="inlineStr"/>
-      <c r="CJ42" t="inlineStr"/>
-      <c r="CK42" t="inlineStr"/>
-      <c r="CL42" t="inlineStr"/>
-      <c r="CM42" t="inlineStr"/>
-      <c r="CN42" t="inlineStr"/>
-      <c r="CO42" t="inlineStr"/>
-      <c r="CP42" t="inlineStr"/>
-      <c r="CQ42" t="inlineStr"/>
-      <c r="CR42" t="inlineStr"/>
-      <c r="CS42" t="inlineStr"/>
-      <c r="CT42" t="inlineStr"/>
-      <c r="CU42" t="inlineStr"/>
-      <c r="CV42" t="inlineStr"/>
-      <c r="CW42" t="inlineStr"/>
-      <c r="CX42" t="inlineStr"/>
-      <c r="CY42" t="inlineStr"/>
-      <c r="CZ42" t="inlineStr"/>
-      <c r="DA42" t="inlineStr"/>
-      <c r="DB42" t="inlineStr"/>
-      <c r="DC42" t="inlineStr"/>
       <c r="DD42" t="n">
         <v>186</v>
       </c>
@@ -14557,11 +12295,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DO42" t="inlineStr"/>
-      <c r="DP42" t="inlineStr"/>
-      <c r="DQ42" t="inlineStr"/>
-      <c r="DR42" t="inlineStr"/>
-      <c r="DS42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14615,7 +12348,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -14687,7 +12419,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -14705,13 +12436,6 @@
       <c r="AK43" t="n">
         <v>11</v>
       </c>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr"/>
       <c r="AS43" t="n">
         <v>1300000</v>
       </c>
@@ -14730,11 +12454,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
-      <c r="BA43" t="inlineStr"/>
       <c r="BB43" t="n">
         <v>7.7</v>
       </c>
@@ -14780,47 +12499,17 @@
       <c r="BN43" t="n">
         <v>0.29</v>
       </c>
-      <c r="BO43" t="inlineStr"/>
-      <c r="BP43" t="inlineStr"/>
-      <c r="BQ43" t="inlineStr"/>
-      <c r="BR43" t="inlineStr"/>
-      <c r="BS43" t="inlineStr"/>
-      <c r="BT43" t="inlineStr"/>
-      <c r="BU43" t="inlineStr"/>
-      <c r="BV43" t="inlineStr"/>
-      <c r="BW43" t="inlineStr"/>
-      <c r="BX43" t="inlineStr"/>
-      <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="n">
         <v>100</v>
       </c>
       <c r="CA43" t="n">
         <v>186418353</v>
       </c>
-      <c r="CB43" t="inlineStr"/>
-      <c r="CC43" t="inlineStr"/>
-      <c r="CD43" t="inlineStr"/>
-      <c r="CE43" t="inlineStr"/>
       <c r="CF43" t="inlineStr">
         <is>
           <t>HomeGoods (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG43" t="inlineStr"/>
-      <c r="CH43" t="inlineStr"/>
-      <c r="CI43" t="inlineStr"/>
-      <c r="CJ43" t="inlineStr"/>
-      <c r="CK43" t="inlineStr"/>
-      <c r="CL43" t="inlineStr"/>
-      <c r="CM43" t="inlineStr"/>
-      <c r="CN43" t="inlineStr"/>
-      <c r="CO43" t="inlineStr"/>
-      <c r="CP43" t="inlineStr"/>
-      <c r="CQ43" t="inlineStr"/>
-      <c r="CR43" t="inlineStr"/>
-      <c r="CS43" t="inlineStr"/>
-      <c r="CT43" t="inlineStr"/>
-      <c r="CU43" t="inlineStr"/>
       <c r="CV43" t="inlineStr">
         <is>
           <t>Community</t>
@@ -14853,22 +12542,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DD43" t="inlineStr"/>
-      <c r="DE43" t="inlineStr"/>
-      <c r="DF43" t="inlineStr"/>
-      <c r="DG43" t="inlineStr"/>
-      <c r="DH43" t="inlineStr"/>
-      <c r="DI43" t="inlineStr"/>
-      <c r="DJ43" t="inlineStr"/>
-      <c r="DK43" t="inlineStr"/>
-      <c r="DL43" t="inlineStr"/>
-      <c r="DM43" t="inlineStr"/>
-      <c r="DN43" t="inlineStr"/>
-      <c r="DO43" t="inlineStr"/>
-      <c r="DP43" t="inlineStr"/>
-      <c r="DQ43" t="inlineStr"/>
-      <c r="DR43" t="inlineStr"/>
-      <c r="DS43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14922,7 +12595,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -14947,7 +12619,6 @@
       <c r="R44" t="n">
         <v>2003</v>
       </c>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
         <v>1</v>
       </c>
@@ -14965,9 +12636,6 @@
       <c r="X44" t="n">
         <v>7.56</v>
       </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="n">
         <v>1198</v>
       </c>
@@ -14984,7 +12652,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -15002,10 +12669,6 @@
       <c r="AK44" t="n">
         <v>30</v>
       </c>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr">
         <is>
           <t>Gateway Build Co.</t>
@@ -15021,15 +12684,6 @@
           <t>2027-Q1</t>
         </is>
       </c>
-      <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr"/>
-      <c r="AX44" t="inlineStr"/>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr"/>
-      <c r="BA44" t="inlineStr"/>
       <c r="BB44" t="n">
         <v>4.3</v>
       </c>
@@ -15075,31 +12729,9 @@
       <c r="BN44" t="n">
         <v>1.97</v>
       </c>
-      <c r="BO44" t="inlineStr"/>
-      <c r="BP44" t="inlineStr"/>
-      <c r="BQ44" t="inlineStr"/>
-      <c r="BR44" t="inlineStr"/>
-      <c r="BS44" t="inlineStr"/>
-      <c r="BT44" t="inlineStr"/>
-      <c r="BU44" t="inlineStr"/>
-      <c r="BV44" t="inlineStr"/>
-      <c r="BW44" t="inlineStr"/>
-      <c r="BX44" t="inlineStr"/>
-      <c r="BY44" t="inlineStr"/>
       <c r="BZ44" t="n">
         <v>100</v>
       </c>
-      <c r="CA44" t="inlineStr"/>
-      <c r="CB44" t="inlineStr"/>
-      <c r="CC44" t="inlineStr"/>
-      <c r="CD44" t="inlineStr"/>
-      <c r="CE44" t="inlineStr"/>
-      <c r="CF44" t="inlineStr"/>
-      <c r="CG44" t="inlineStr"/>
-      <c r="CH44" t="inlineStr"/>
-      <c r="CI44" t="inlineStr"/>
-      <c r="CJ44" t="inlineStr"/>
-      <c r="CK44" t="inlineStr"/>
       <c r="CL44" t="n">
         <v>36</v>
       </c>
@@ -15136,30 +12768,6 @@
       <c r="CU44" t="n">
         <v>135</v>
       </c>
-      <c r="CV44" t="inlineStr"/>
-      <c r="CW44" t="inlineStr"/>
-      <c r="CX44" t="inlineStr"/>
-      <c r="CY44" t="inlineStr"/>
-      <c r="CZ44" t="inlineStr"/>
-      <c r="DA44" t="inlineStr"/>
-      <c r="DB44" t="inlineStr"/>
-      <c r="DC44" t="inlineStr"/>
-      <c r="DD44" t="inlineStr"/>
-      <c r="DE44" t="inlineStr"/>
-      <c r="DF44" t="inlineStr"/>
-      <c r="DG44" t="inlineStr"/>
-      <c r="DH44" t="inlineStr"/>
-      <c r="DI44" t="inlineStr"/>
-      <c r="DJ44" t="inlineStr"/>
-      <c r="DK44" t="inlineStr"/>
-      <c r="DL44" t="inlineStr"/>
-      <c r="DM44" t="inlineStr"/>
-      <c r="DN44" t="inlineStr"/>
-      <c r="DO44" t="inlineStr"/>
-      <c r="DP44" t="inlineStr"/>
-      <c r="DQ44" t="inlineStr"/>
-      <c r="DR44" t="inlineStr"/>
-      <c r="DS44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -15213,7 +12821,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Under Construction</t>
@@ -15285,7 +12892,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -15303,10 +12909,6 @@
       <c r="AK45" t="n">
         <v>1</v>
       </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr">
         <is>
           <t>North Fund Development</t>
@@ -15340,11 +12942,6 @@
           <t>Mall Street Partners</t>
         </is>
       </c>
-      <c r="AW45" t="inlineStr"/>
-      <c r="AX45" t="inlineStr"/>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
       <c r="BB45" t="n">
         <v>3.9</v>
       </c>
@@ -15390,43 +12987,12 @@
       <c r="BN45" t="n">
         <v>1.03</v>
       </c>
-      <c r="BO45" t="inlineStr"/>
-      <c r="BP45" t="inlineStr"/>
-      <c r="BQ45" t="inlineStr"/>
-      <c r="BR45" t="inlineStr"/>
-      <c r="BS45" t="inlineStr"/>
-      <c r="BT45" t="inlineStr"/>
-      <c r="BU45" t="inlineStr"/>
-      <c r="BV45" t="inlineStr"/>
-      <c r="BW45" t="inlineStr"/>
-      <c r="BX45" t="inlineStr"/>
-      <c r="BY45" t="inlineStr"/>
       <c r="BZ45" t="n">
         <v>100</v>
       </c>
       <c r="CA45" t="n">
         <v>239108958</v>
       </c>
-      <c r="CB45" t="inlineStr"/>
-      <c r="CC45" t="inlineStr"/>
-      <c r="CD45" t="inlineStr"/>
-      <c r="CE45" t="inlineStr"/>
-      <c r="CF45" t="inlineStr"/>
-      <c r="CG45" t="inlineStr"/>
-      <c r="CH45" t="inlineStr"/>
-      <c r="CI45" t="inlineStr"/>
-      <c r="CJ45" t="inlineStr"/>
-      <c r="CK45" t="inlineStr"/>
-      <c r="CL45" t="inlineStr"/>
-      <c r="CM45" t="inlineStr"/>
-      <c r="CN45" t="inlineStr"/>
-      <c r="CO45" t="inlineStr"/>
-      <c r="CP45" t="inlineStr"/>
-      <c r="CQ45" t="inlineStr"/>
-      <c r="CR45" t="inlineStr"/>
-      <c r="CS45" t="inlineStr"/>
-      <c r="CT45" t="inlineStr"/>
-      <c r="CU45" t="inlineStr"/>
       <c r="CV45" t="inlineStr">
         <is>
           <t>Community</t>
@@ -15459,22 +13025,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD45" t="inlineStr"/>
-      <c r="DE45" t="inlineStr"/>
-      <c r="DF45" t="inlineStr"/>
-      <c r="DG45" t="inlineStr"/>
-      <c r="DH45" t="inlineStr"/>
-      <c r="DI45" t="inlineStr"/>
-      <c r="DJ45" t="inlineStr"/>
-      <c r="DK45" t="inlineStr"/>
-      <c r="DL45" t="inlineStr"/>
-      <c r="DM45" t="inlineStr"/>
-      <c r="DN45" t="inlineStr"/>
-      <c r="DO45" t="inlineStr"/>
-      <c r="DP45" t="inlineStr"/>
-      <c r="DQ45" t="inlineStr"/>
-      <c r="DR45" t="inlineStr"/>
-      <c r="DS45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -15528,11 +13078,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Northeast</t>
-        </is>
-      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -15574,7 +13119,6 @@
           <t>NNN</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="n">
         <v>206000000</v>
       </c>
@@ -15602,7 +13146,6 @@
           <t>Riverbend Residential</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -15620,13 +13163,6 @@
       <c r="AK46" t="n">
         <v>1</v>
       </c>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr"/>
       <c r="AS46" t="n">
         <v>2350000</v>
       </c>
@@ -15714,8 +13250,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP46" t="inlineStr"/>
-      <c r="BQ46" t="inlineStr"/>
       <c r="BR46" t="n">
         <v>25</v>
       </c>
@@ -15754,16 +13288,6 @@
       <c r="CA46" t="n">
         <v>229001441</v>
       </c>
-      <c r="CB46" t="inlineStr"/>
-      <c r="CC46" t="inlineStr"/>
-      <c r="CD46" t="inlineStr"/>
-      <c r="CE46" t="inlineStr"/>
-      <c r="CF46" t="inlineStr"/>
-      <c r="CG46" t="inlineStr"/>
-      <c r="CH46" t="inlineStr"/>
-      <c r="CI46" t="inlineStr"/>
-      <c r="CJ46" t="inlineStr"/>
-      <c r="CK46" t="inlineStr"/>
       <c r="CL46" t="n">
         <v>20</v>
       </c>
@@ -15800,30 +13324,6 @@
       <c r="CU46" t="n">
         <v>90</v>
       </c>
-      <c r="CV46" t="inlineStr"/>
-      <c r="CW46" t="inlineStr"/>
-      <c r="CX46" t="inlineStr"/>
-      <c r="CY46" t="inlineStr"/>
-      <c r="CZ46" t="inlineStr"/>
-      <c r="DA46" t="inlineStr"/>
-      <c r="DB46" t="inlineStr"/>
-      <c r="DC46" t="inlineStr"/>
-      <c r="DD46" t="inlineStr"/>
-      <c r="DE46" t="inlineStr"/>
-      <c r="DF46" t="inlineStr"/>
-      <c r="DG46" t="inlineStr"/>
-      <c r="DH46" t="inlineStr"/>
-      <c r="DI46" t="inlineStr"/>
-      <c r="DJ46" t="inlineStr"/>
-      <c r="DK46" t="inlineStr"/>
-      <c r="DL46" t="inlineStr"/>
-      <c r="DM46" t="inlineStr"/>
-      <c r="DN46" t="inlineStr"/>
-      <c r="DO46" t="inlineStr"/>
-      <c r="DP46" t="inlineStr"/>
-      <c r="DQ46" t="inlineStr"/>
-      <c r="DR46" t="inlineStr"/>
-      <c r="DS46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15877,7 +13377,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -15902,7 +13401,6 @@
       <c r="R47" t="n">
         <v>1970</v>
       </c>
-      <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
         <v>1</v>
       </c>
@@ -15947,7 +13445,6 @@
           <t>SouthPoint Advisors</t>
         </is>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -15965,15 +13462,6 @@
       <c r="AK47" t="n">
         <v>1</v>
       </c>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="inlineStr"/>
       <c r="AU47" t="inlineStr">
         <is>
           <t>SouthPoint Advisors</t>
@@ -16053,8 +13541,6 @@
           <t>Fixed</t>
         </is>
       </c>
-      <c r="BP47" t="inlineStr"/>
-      <c r="BQ47" t="inlineStr"/>
       <c r="BR47" t="n">
         <v>0</v>
       </c>
@@ -16093,16 +13579,6 @@
       <c r="CA47" t="n">
         <v>274281537</v>
       </c>
-      <c r="CB47" t="inlineStr"/>
-      <c r="CC47" t="inlineStr"/>
-      <c r="CD47" t="inlineStr"/>
-      <c r="CE47" t="inlineStr"/>
-      <c r="CF47" t="inlineStr"/>
-      <c r="CG47" t="inlineStr"/>
-      <c r="CH47" t="inlineStr"/>
-      <c r="CI47" t="inlineStr"/>
-      <c r="CJ47" t="inlineStr"/>
-      <c r="CK47" t="inlineStr"/>
       <c r="CL47" t="n">
         <v>22</v>
       </c>
@@ -16139,30 +13615,6 @@
       <c r="CU47" t="n">
         <v>130</v>
       </c>
-      <c r="CV47" t="inlineStr"/>
-      <c r="CW47" t="inlineStr"/>
-      <c r="CX47" t="inlineStr"/>
-      <c r="CY47" t="inlineStr"/>
-      <c r="CZ47" t="inlineStr"/>
-      <c r="DA47" t="inlineStr"/>
-      <c r="DB47" t="inlineStr"/>
-      <c r="DC47" t="inlineStr"/>
-      <c r="DD47" t="inlineStr"/>
-      <c r="DE47" t="inlineStr"/>
-      <c r="DF47" t="inlineStr"/>
-      <c r="DG47" t="inlineStr"/>
-      <c r="DH47" t="inlineStr"/>
-      <c r="DI47" t="inlineStr"/>
-      <c r="DJ47" t="inlineStr"/>
-      <c r="DK47" t="inlineStr"/>
-      <c r="DL47" t="inlineStr"/>
-      <c r="DM47" t="inlineStr"/>
-      <c r="DN47" t="inlineStr"/>
-      <c r="DO47" t="inlineStr"/>
-      <c r="DP47" t="inlineStr"/>
-      <c r="DQ47" t="inlineStr"/>
-      <c r="DR47" t="inlineStr"/>
-      <c r="DS47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16216,7 +13668,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Under Construction</t>
@@ -16241,7 +13692,6 @@
       <c r="R48" t="n">
         <v>1981</v>
       </c>
-      <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
         <v>2</v>
       </c>
@@ -16286,7 +13736,6 @@
           <t>Twin Cities Ventures</t>
         </is>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -16335,8 +13784,6 @@
           <t>2027-Q1</t>
         </is>
       </c>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="inlineStr"/>
       <c r="AU48" t="inlineStr">
         <is>
           <t>Twin Cities Ventures</t>
@@ -16347,11 +13794,6 @@
           <t>Heartland REIT</t>
         </is>
       </c>
-      <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr"/>
-      <c r="BA48" t="inlineStr"/>
       <c r="BB48" t="n">
         <v>4</v>
       </c>
@@ -16397,43 +13839,12 @@
       <c r="BN48" t="n">
         <v>1.03</v>
       </c>
-      <c r="BO48" t="inlineStr"/>
-      <c r="BP48" t="inlineStr"/>
-      <c r="BQ48" t="inlineStr"/>
-      <c r="BR48" t="inlineStr"/>
-      <c r="BS48" t="inlineStr"/>
-      <c r="BT48" t="inlineStr"/>
-      <c r="BU48" t="inlineStr"/>
-      <c r="BV48" t="inlineStr"/>
-      <c r="BW48" t="inlineStr"/>
-      <c r="BX48" t="inlineStr"/>
-      <c r="BY48" t="inlineStr"/>
       <c r="BZ48" t="n">
         <v>100</v>
       </c>
       <c r="CA48" t="n">
         <v>95127964</v>
       </c>
-      <c r="CB48" t="inlineStr"/>
-      <c r="CC48" t="inlineStr"/>
-      <c r="CD48" t="inlineStr"/>
-      <c r="CE48" t="inlineStr"/>
-      <c r="CF48" t="inlineStr"/>
-      <c r="CG48" t="inlineStr"/>
-      <c r="CH48" t="inlineStr"/>
-      <c r="CI48" t="inlineStr"/>
-      <c r="CJ48" t="inlineStr"/>
-      <c r="CK48" t="inlineStr"/>
-      <c r="CL48" t="inlineStr"/>
-      <c r="CM48" t="inlineStr"/>
-      <c r="CN48" t="inlineStr"/>
-      <c r="CO48" t="inlineStr"/>
-      <c r="CP48" t="inlineStr"/>
-      <c r="CQ48" t="inlineStr"/>
-      <c r="CR48" t="inlineStr"/>
-      <c r="CS48" t="inlineStr"/>
-      <c r="CT48" t="inlineStr"/>
-      <c r="CU48" t="inlineStr"/>
       <c r="CV48" t="inlineStr">
         <is>
           <t>Neighborhood</t>
@@ -16466,22 +13877,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="DD48" t="inlineStr"/>
-      <c r="DE48" t="inlineStr"/>
-      <c r="DF48" t="inlineStr"/>
-      <c r="DG48" t="inlineStr"/>
-      <c r="DH48" t="inlineStr"/>
-      <c r="DI48" t="inlineStr"/>
-      <c r="DJ48" t="inlineStr"/>
-      <c r="DK48" t="inlineStr"/>
-      <c r="DL48" t="inlineStr"/>
-      <c r="DM48" t="inlineStr"/>
-      <c r="DN48" t="inlineStr"/>
-      <c r="DO48" t="inlineStr"/>
-      <c r="DP48" t="inlineStr"/>
-      <c r="DQ48" t="inlineStr"/>
-      <c r="DR48" t="inlineStr"/>
-      <c r="DS48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16535,7 +13930,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16560,7 +13954,6 @@
       <c r="R49" t="n">
         <v>2008</v>
       </c>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="n">
         <v>2</v>
       </c>
@@ -16605,7 +13998,6 @@
           <t>Gateway Industrial REIT</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -16639,11 +14031,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="AP49" t="inlineStr"/>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr"/>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="inlineStr"/>
       <c r="AU49" t="inlineStr">
         <is>
           <t>Gateway Industrial REIT</t>
@@ -16654,11 +14041,6 @@
           <t>North Fund IV</t>
         </is>
       </c>
-      <c r="AW49" t="inlineStr"/>
-      <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
-      <c r="BA49" t="inlineStr"/>
       <c r="BB49" t="n">
         <v>7.5</v>
       </c>
@@ -16704,47 +14086,17 @@
       <c r="BN49" t="n">
         <v>0.74</v>
       </c>
-      <c r="BO49" t="inlineStr"/>
-      <c r="BP49" t="inlineStr"/>
-      <c r="BQ49" t="inlineStr"/>
-      <c r="BR49" t="inlineStr"/>
-      <c r="BS49" t="inlineStr"/>
-      <c r="BT49" t="inlineStr"/>
-      <c r="BU49" t="inlineStr"/>
-      <c r="BV49" t="inlineStr"/>
-      <c r="BW49" t="inlineStr"/>
-      <c r="BX49" t="inlineStr"/>
-      <c r="BY49" t="inlineStr"/>
       <c r="BZ49" t="n">
         <v>100</v>
       </c>
       <c r="CA49" t="n">
         <v>312244194</v>
       </c>
-      <c r="CB49" t="inlineStr"/>
-      <c r="CC49" t="inlineStr"/>
-      <c r="CD49" t="inlineStr"/>
-      <c r="CE49" t="inlineStr"/>
       <c r="CF49" t="inlineStr">
         <is>
           <t>Lunds &amp; Byerlys (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG49" t="inlineStr"/>
-      <c r="CH49" t="inlineStr"/>
-      <c r="CI49" t="inlineStr"/>
-      <c r="CJ49" t="inlineStr"/>
-      <c r="CK49" t="inlineStr"/>
-      <c r="CL49" t="inlineStr"/>
-      <c r="CM49" t="inlineStr"/>
-      <c r="CN49" t="inlineStr"/>
-      <c r="CO49" t="inlineStr"/>
-      <c r="CP49" t="inlineStr"/>
-      <c r="CQ49" t="inlineStr"/>
-      <c r="CR49" t="inlineStr"/>
-      <c r="CS49" t="inlineStr"/>
-      <c r="CT49" t="inlineStr"/>
-      <c r="CU49" t="inlineStr"/>
       <c r="CV49" t="inlineStr">
         <is>
           <t>Strip</t>
@@ -16777,22 +14129,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD49" t="inlineStr"/>
-      <c r="DE49" t="inlineStr"/>
-      <c r="DF49" t="inlineStr"/>
-      <c r="DG49" t="inlineStr"/>
-      <c r="DH49" t="inlineStr"/>
-      <c r="DI49" t="inlineStr"/>
-      <c r="DJ49" t="inlineStr"/>
-      <c r="DK49" t="inlineStr"/>
-      <c r="DL49" t="inlineStr"/>
-      <c r="DM49" t="inlineStr"/>
-      <c r="DN49" t="inlineStr"/>
-      <c r="DO49" t="inlineStr"/>
-      <c r="DP49" t="inlineStr"/>
-      <c r="DQ49" t="inlineStr"/>
-      <c r="DR49" t="inlineStr"/>
-      <c r="DS49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16846,7 +14182,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -16871,7 +14206,6 @@
       <c r="R50" t="n">
         <v>1968</v>
       </c>
-      <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
         <v>2</v>
       </c>
@@ -16889,9 +14223,6 @@
       <c r="X50" t="n">
         <v>5.03</v>
       </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="n">
         <v>631</v>
       </c>
@@ -16908,7 +14239,6 @@
           <t>Sample Holdings LLC</t>
         </is>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -16942,13 +14272,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
           <t>Sample CMBS 2023-C1</t>
@@ -17061,27 +14384,6 @@
       <c r="BZ50" t="n">
         <v>75</v>
       </c>
-      <c r="CA50" t="inlineStr"/>
-      <c r="CB50" t="inlineStr"/>
-      <c r="CC50" t="inlineStr"/>
-      <c r="CD50" t="inlineStr"/>
-      <c r="CE50" t="inlineStr"/>
-      <c r="CF50" t="inlineStr"/>
-      <c r="CG50" t="inlineStr"/>
-      <c r="CH50" t="inlineStr"/>
-      <c r="CI50" t="inlineStr"/>
-      <c r="CJ50" t="inlineStr"/>
-      <c r="CK50" t="inlineStr"/>
-      <c r="CL50" t="inlineStr"/>
-      <c r="CM50" t="inlineStr"/>
-      <c r="CN50" t="inlineStr"/>
-      <c r="CO50" t="inlineStr"/>
-      <c r="CP50" t="inlineStr"/>
-      <c r="CQ50" t="inlineStr"/>
-      <c r="CR50" t="inlineStr"/>
-      <c r="CS50" t="inlineStr"/>
-      <c r="CT50" t="inlineStr"/>
-      <c r="CU50" t="inlineStr"/>
       <c r="CV50" t="inlineStr">
         <is>
           <t>Neighborhood</t>
@@ -17114,22 +14416,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD50" t="inlineStr"/>
-      <c r="DE50" t="inlineStr"/>
-      <c r="DF50" t="inlineStr"/>
-      <c r="DG50" t="inlineStr"/>
-      <c r="DH50" t="inlineStr"/>
-      <c r="DI50" t="inlineStr"/>
-      <c r="DJ50" t="inlineStr"/>
-      <c r="DK50" t="inlineStr"/>
-      <c r="DL50" t="inlineStr"/>
-      <c r="DM50" t="inlineStr"/>
-      <c r="DN50" t="inlineStr"/>
-      <c r="DO50" t="inlineStr"/>
-      <c r="DP50" t="inlineStr"/>
-      <c r="DQ50" t="inlineStr"/>
-      <c r="DR50" t="inlineStr"/>
-      <c r="DS50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17183,7 +14469,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -17225,7 +14510,6 @@
           <t>NNN</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
       <c r="Y51" t="n">
         <v>106000000</v>
       </c>
@@ -17253,7 +14537,6 @@
           <t>Gateway Industrial REIT</t>
         </is>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -17287,9 +14570,6 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="n">
         <v>3625000</v>
       </c>
@@ -17423,30 +14703,11 @@
       <c r="CA51" t="n">
         <v>110426034</v>
       </c>
-      <c r="CB51" t="inlineStr"/>
-      <c r="CC51" t="inlineStr"/>
-      <c r="CD51" t="inlineStr"/>
-      <c r="CE51" t="inlineStr"/>
       <c r="CF51" t="inlineStr">
         <is>
           <t>Lunds &amp; Byerlys (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG51" t="inlineStr"/>
-      <c r="CH51" t="inlineStr"/>
-      <c r="CI51" t="inlineStr"/>
-      <c r="CJ51" t="inlineStr"/>
-      <c r="CK51" t="inlineStr"/>
-      <c r="CL51" t="inlineStr"/>
-      <c r="CM51" t="inlineStr"/>
-      <c r="CN51" t="inlineStr"/>
-      <c r="CO51" t="inlineStr"/>
-      <c r="CP51" t="inlineStr"/>
-      <c r="CQ51" t="inlineStr"/>
-      <c r="CR51" t="inlineStr"/>
-      <c r="CS51" t="inlineStr"/>
-      <c r="CT51" t="inlineStr"/>
-      <c r="CU51" t="inlineStr"/>
       <c r="CV51" t="inlineStr">
         <is>
           <t>Strip</t>
@@ -17479,22 +14740,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD51" t="inlineStr"/>
-      <c r="DE51" t="inlineStr"/>
-      <c r="DF51" t="inlineStr"/>
-      <c r="DG51" t="inlineStr"/>
-      <c r="DH51" t="inlineStr"/>
-      <c r="DI51" t="inlineStr"/>
-      <c r="DJ51" t="inlineStr"/>
-      <c r="DK51" t="inlineStr"/>
-      <c r="DL51" t="inlineStr"/>
-      <c r="DM51" t="inlineStr"/>
-      <c r="DN51" t="inlineStr"/>
-      <c r="DO51" t="inlineStr"/>
-      <c r="DP51" t="inlineStr"/>
-      <c r="DQ51" t="inlineStr"/>
-      <c r="DR51" t="inlineStr"/>
-      <c r="DS51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17548,7 +14793,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Existing</t>
@@ -17573,7 +14817,6 @@
       <c r="R52" t="n">
         <v>2003</v>
       </c>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
         <v>1</v>
       </c>
@@ -17618,7 +14861,6 @@
           <t>Capitol City Assets</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr">
         <is>
           <t>Fictional sample record for platform demo.</t>
@@ -17636,15 +14878,6 @@
       <c r="AK52" t="n">
         <v>1</v>
       </c>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="inlineStr"/>
-      <c r="AQ52" t="inlineStr"/>
-      <c r="AR52" t="inlineStr"/>
-      <c r="AS52" t="inlineStr"/>
-      <c r="AT52" t="inlineStr"/>
       <c r="AU52" t="inlineStr">
         <is>
           <t>Capitol City Assets</t>
@@ -17759,37 +14992,17 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="BY52" t="inlineStr"/>
       <c r="BZ52" t="n">
         <v>100</v>
       </c>
       <c r="CA52" t="n">
         <v>17174080</v>
       </c>
-      <c r="CB52" t="inlineStr"/>
-      <c r="CC52" t="inlineStr"/>
-      <c r="CD52" t="inlineStr"/>
-      <c r="CE52" t="inlineStr"/>
       <c r="CF52" t="inlineStr">
         <is>
           <t>HomeGoods (SAMPLE)</t>
         </is>
       </c>
-      <c r="CG52" t="inlineStr"/>
-      <c r="CH52" t="inlineStr"/>
-      <c r="CI52" t="inlineStr"/>
-      <c r="CJ52" t="inlineStr"/>
-      <c r="CK52" t="inlineStr"/>
-      <c r="CL52" t="inlineStr"/>
-      <c r="CM52" t="inlineStr"/>
-      <c r="CN52" t="inlineStr"/>
-      <c r="CO52" t="inlineStr"/>
-      <c r="CP52" t="inlineStr"/>
-      <c r="CQ52" t="inlineStr"/>
-      <c r="CR52" t="inlineStr"/>
-      <c r="CS52" t="inlineStr"/>
-      <c r="CT52" t="inlineStr"/>
-      <c r="CU52" t="inlineStr"/>
       <c r="CV52" t="inlineStr">
         <is>
           <t>Lifestyle</t>
@@ -17822,22 +15035,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="DD52" t="inlineStr"/>
-      <c r="DE52" t="inlineStr"/>
-      <c r="DF52" t="inlineStr"/>
-      <c r="DG52" t="inlineStr"/>
-      <c r="DH52" t="inlineStr"/>
-      <c r="DI52" t="inlineStr"/>
-      <c r="DJ52" t="inlineStr"/>
-      <c r="DK52" t="inlineStr"/>
-      <c r="DL52" t="inlineStr"/>
-      <c r="DM52" t="inlineStr"/>
-      <c r="DN52" t="inlineStr"/>
-      <c r="DO52" t="inlineStr"/>
-      <c r="DP52" t="inlineStr"/>
-      <c r="DQ52" t="inlineStr"/>
-      <c r="DR52" t="inlineStr"/>
-      <c r="DS52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/properties.xlsx
+++ b/data/properties.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS52"/>
+  <dimension ref="A1:DX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1167,6 +1167,31 @@
           <t>Proposed Use</t>
         </is>
       </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>Source Detail</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>As-of Date</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Last Verified</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1417,6 +1442,27 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1669,6 +1715,31 @@
           <t>Underground</t>
         </is>
       </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2000,6 +2071,31 @@
           <t>Surface</t>
         </is>
       </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>2025-02-15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2305,6 +2401,31 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2542,6 +2663,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2838,6 +2984,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3079,6 +3250,27 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3380,6 +3572,31 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>Public record</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>County records</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3616,6 +3833,27 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3940,6 +4178,31 @@
           <t>Surface</t>
         </is>
       </c>
+      <c r="DT11" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU11" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV11" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4256,6 +4519,31 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT12" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU12" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV12" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW12" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4527,6 +4815,27 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT13" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU13" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV13" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW13" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="DX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4802,6 +5111,27 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT14" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU14" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV14" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW14" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5059,6 +5389,31 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT15" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU15" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV15" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW15" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="DX15" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5348,6 +5703,31 @@
           <t>Underground</t>
         </is>
       </c>
+      <c r="DT16" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU16" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV16" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW16" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="DX16" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5631,6 +6011,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT17" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU17" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV17" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW17" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="DX17" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5946,6 +6351,27 @@
       <c r="CU18" t="n">
         <v>130</v>
       </c>
+      <c r="DT18" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU18" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV18" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW18" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6209,6 +6635,27 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT19" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU19" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV19" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="DX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6500,6 +6947,27 @@
       <c r="CU20" t="n">
         <v>185</v>
       </c>
+      <c r="DT20" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU20" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV20" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6805,6 +7273,31 @@
       <c r="CU21" t="n">
         <v>110</v>
       </c>
+      <c r="DT21" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU21" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV21" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW21" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6933,6 +7426,31 @@
           <t>Industrial</t>
         </is>
       </c>
+      <c r="DT22" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU22" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV22" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW22" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="DX22" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7173,6 +7691,31 @@
       <c r="CU23" t="n">
         <v>90</v>
       </c>
+      <c r="DT23" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU23" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV23" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7446,6 +7989,31 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT24" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU24" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV24" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW24" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="DX24" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7754,6 +8322,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT25" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU25" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV25" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW25" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
+      <c r="DX25" t="inlineStr">
+        <is>
+          <t>2024-11-15</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8045,6 +8638,31 @@
       <c r="CU26" t="n">
         <v>185</v>
       </c>
+      <c r="DT26" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU26" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV26" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW26" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="DX26" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8302,6 +8920,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT27" t="inlineStr">
+        <is>
+          <t>Public record</t>
+        </is>
+      </c>
+      <c r="DU27" t="inlineStr">
+        <is>
+          <t>County records</t>
+        </is>
+      </c>
+      <c r="DV27" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW27" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8593,6 +9236,31 @@
       <c r="CU28" t="n">
         <v>185</v>
       </c>
+      <c r="DT28" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU28" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV28" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW28" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="DX28" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8906,6 +9574,31 @@
           <t>Underground</t>
         </is>
       </c>
+      <c r="DT29" t="inlineStr">
+        <is>
+          <t>Public record</t>
+        </is>
+      </c>
+      <c r="DU29" t="inlineStr">
+        <is>
+          <t>County records</t>
+        </is>
+      </c>
+      <c r="DV29" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW29" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="DX29" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9142,6 +9835,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT30" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU30" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV30" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="DX30" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9270,6 +9988,27 @@
           <t>Mixed-Use</t>
         </is>
       </c>
+      <c r="DT31" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU31" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV31" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW31" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="DX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9558,6 +10297,27 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT32" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU32" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV32" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW32" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="DX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9865,6 +10625,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT33" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU33" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV33" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW33" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="DX33" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10106,6 +10891,27 @@
           <t>Structured</t>
         </is>
       </c>
+      <c r="DT34" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU34" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV34" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW34" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="DX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10425,6 +11231,31 @@
           <t>Underground</t>
         </is>
       </c>
+      <c r="DT35" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU35" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV35" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="DX35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10532,6 +11363,31 @@
           <t>Data Center</t>
         </is>
       </c>
+      <c r="DT36" t="inlineStr">
+        <is>
+          <t>Public record</t>
+        </is>
+      </c>
+      <c r="DU36" t="inlineStr">
+        <is>
+          <t>County records</t>
+        </is>
+      </c>
+      <c r="DV36" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW36" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="DX36" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10847,6 +11703,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT37" t="inlineStr">
+        <is>
+          <t>Public record</t>
+        </is>
+      </c>
+      <c r="DU37" t="inlineStr">
+        <is>
+          <t>County records</t>
+        </is>
+      </c>
+      <c r="DV37" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW37" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="DX37" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11157,6 +12038,31 @@
       <c r="CU38" t="n">
         <v>135</v>
       </c>
+      <c r="DT38" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU38" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV38" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW38" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="DX38" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11442,6 +12348,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT39" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU39" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV39" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW39" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="DX39" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11749,6 +12680,31 @@
       <c r="CU40" t="n">
         <v>110</v>
       </c>
+      <c r="DT40" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU40" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV40" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW40" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="DX40" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12012,6 +12968,27 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT41" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU41" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV41" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW41" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="DX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12295,6 +13272,27 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT42" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU42" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV42" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW42" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="DX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12542,6 +13540,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT43" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU43" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV43" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW43" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="DX43" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12768,6 +13791,31 @@
       <c r="CU44" t="n">
         <v>135</v>
       </c>
+      <c r="DT44" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU44" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV44" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW44" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="DX44" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -13025,6 +14073,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT45" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU45" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV45" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW45" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="DX45" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -13324,6 +14397,31 @@
       <c r="CU46" t="n">
         <v>90</v>
       </c>
+      <c r="DT46" t="inlineStr">
+        <is>
+          <t>First-hand (our deal)</t>
+        </is>
+      </c>
+      <c r="DU46" t="inlineStr">
+        <is>
+          <t>Our transaction file</t>
+        </is>
+      </c>
+      <c r="DV46" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW46" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="DX46" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13615,6 +14713,27 @@
       <c r="CU47" t="n">
         <v>130</v>
       </c>
+      <c r="DT47" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU47" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV47" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW47" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="DX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -13877,6 +14996,31 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="DT48" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU48" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV48" t="inlineStr">
+        <is>
+          <t>Likely</t>
+        </is>
+      </c>
+      <c r="DW48" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="DX48" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14129,6 +15273,27 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT49" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="DU49" t="inlineStr">
+        <is>
+          <t>Broker OM / call</t>
+        </is>
+      </c>
+      <c r="DV49" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW49" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="DX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14416,6 +15581,31 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT50" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU50" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV50" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW50" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
+      <c r="DX50" t="inlineStr">
+        <is>
+          <t>2025-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14740,6 +15930,27 @@
           <t>No</t>
         </is>
       </c>
+      <c r="DT51" t="inlineStr">
+        <is>
+          <t>Counterparty</t>
+        </is>
+      </c>
+      <c r="DU51" t="inlineStr">
+        <is>
+          <t>Seller/buyer rep call</t>
+        </is>
+      </c>
+      <c r="DV51" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="DW51" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="DX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15033,6 +16244,31 @@
       <c r="DC52" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+      <c r="DT52" t="inlineStr">
+        <is>
+          <t>Market hearsay</t>
+        </is>
+      </c>
+      <c r="DU52" t="inlineStr">
+        <is>
+          <t>Industry conversation</t>
+        </is>
+      </c>
+      <c r="DV52" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="DW52" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
+        </is>
+      </c>
+      <c r="DX52" t="inlineStr">
+        <is>
+          <t>2025-01-15</t>
         </is>
       </c>
     </row>
